--- a/data/KP Pesach List 5786.xlsx
+++ b/data/KP Pesach List 5786.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82602666e60ae568/Documents/kp-pesach-orders/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{9BEDD0A3-C321-47F6-BE36-9DD7BEBCADDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79CE3266-7B27-48F1-A2CD-CD23D6944A80}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{9BEDD0A3-C321-47F6-BE36-9DD7BEBCADDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D34F8BF-7CF1-4C56-9085-67F46D0BD5D4}"/>
   <bookViews>
-    <workbookView xWindow="2076" yWindow="2076" windowWidth="17280" windowHeight="8904" xr2:uid="{6BCD7493-0B6E-4B5E-B8CA-70042B6C28AE}"/>
+    <workbookView xWindow="11442" yWindow="0" windowWidth="11676" windowHeight="12318" xr2:uid="{6BCD7493-0B6E-4B5E-B8CA-70042B6C28AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="1702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2805" uniqueCount="1713">
   <si>
     <t>Product</t>
   </si>
@@ -5826,6 +5826,39 @@
       </rPr>
       <t>K</t>
     </r>
+  </si>
+  <si>
+    <t>Beetroot Salad</t>
+  </si>
+  <si>
+    <t>Carrot Salad</t>
+  </si>
+  <si>
+    <t>Butternut Squash and Sweet Potato Soup</t>
+  </si>
+  <si>
+    <t>Vegetable Soup</t>
+  </si>
+  <si>
+    <t>Chicken Soup with Kneidlach</t>
+  </si>
+  <si>
+    <t>Chicken Shawarma</t>
+  </si>
+  <si>
+    <t>Chopped Liver</t>
+  </si>
+  <si>
+    <t>Potato Kugel</t>
+  </si>
+  <si>
+    <t>Ratatouille</t>
+  </si>
+  <si>
+    <t>Roasted Real Vegetables with Balasmic Glaze</t>
+  </si>
+  <si>
+    <t>Roasted Potatoes with Garlic &amp; Rosemary</t>
   </si>
 </sst>
 </file>
@@ -6055,7 +6088,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -6120,6 +6153,20 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6455,8 +6502,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3DF408-6461-4C0D-BAF4-0390C6D1E62E}">
-  <dimension ref="A1:F1502"/>
+  <dimension ref="A1:G1516"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="34.3671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
@@ -16200,25 +16250,21 @@
     </row>
     <row r="1110" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1110" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="B1110" s="4" t="s">
-        <v>11</v>
-      </c>
+        <v>1702</v>
+      </c>
+      <c r="B1110" s="4"/>
       <c r="C1110" s="4"/>
     </row>
     <row r="1111" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1111" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="B1111" s="4" t="s">
-        <v>11</v>
-      </c>
+        <v>1703</v>
+      </c>
+      <c r="B1111" s="4"/>
       <c r="C1111" s="4"/>
     </row>
     <row r="1112" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1112" s="3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B1112" s="4" t="s">
         <v>11</v>
@@ -16227,25 +16273,25 @@
     </row>
     <row r="1113" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1113" s="3" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1113" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C1113" s="4"/>
     </row>
-    <row r="1114" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1114" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1114" s="3" t="s">
-        <v>1546</v>
+        <v>668</v>
       </c>
       <c r="B1114" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C1114" s="4"/>
     </row>
-    <row r="1115" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1115" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1115" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B1115" s="4" t="s">
         <v>11</v>
@@ -16254,70 +16300,70 @@
     </row>
     <row r="1116" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1116" s="3" t="s">
-        <v>671</v>
+        <v>1546</v>
       </c>
       <c r="B1116" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C1116" s="4"/>
     </row>
-    <row r="1117" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1117" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1117" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B1117" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C1117" s="4"/>
     </row>
-    <row r="1118" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1118" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1118" s="3" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B1118" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C1118" s="4"/>
     </row>
-    <row r="1119" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1119" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1119" s="3" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B1119" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C1119" s="4"/>
     </row>
-    <row r="1120" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1120" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1120" s="3" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B1120" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C1120" s="7"/>
+      <c r="C1120" s="4"/>
     </row>
     <row r="1121" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1121" s="3" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B1121" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C1121" s="4"/>
     </row>
-    <row r="1122" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1122" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1122" s="3" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1122" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C1122" s="4"/>
+      <c r="C1122" s="7"/>
     </row>
     <row r="1123" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1123" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B1123" s="4" t="s">
         <v>11</v>
@@ -16326,7 +16372,7 @@
     </row>
     <row r="1124" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1124" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B1124" s="4" t="s">
         <v>11</v>
@@ -16335,7 +16381,7 @@
     </row>
     <row r="1125" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1125" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B1125" s="4" t="s">
         <v>11</v>
@@ -16344,25 +16390,25 @@
     </row>
     <row r="1126" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1126" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B1126" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C1126" s="4"/>
     </row>
-    <row r="1127" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1127" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1127" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1127" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C1127" s="4"/>
     </row>
-    <row r="1128" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1128" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1128" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B1128" s="4" t="s">
         <v>11</v>
@@ -16371,165 +16417,167 @@
     </row>
     <row r="1129" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1129" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="B1129" s="4"/>
+        <v>682</v>
+      </c>
+      <c r="B1129" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="C1129" s="4"/>
     </row>
     <row r="1130" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1130" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="B1130" s="4"/>
+        <v>683</v>
+      </c>
+      <c r="B1130" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="C1130" s="4"/>
     </row>
-    <row r="1131" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1131" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1131" s="3" t="s">
-        <v>685</v>
+        <v>647</v>
       </c>
       <c r="B1131" s="4"/>
       <c r="C1131" s="4"/>
     </row>
     <row r="1132" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1132" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="B1132" s="4" t="s">
-        <v>568</v>
-      </c>
+        <v>684</v>
+      </c>
+      <c r="B1132" s="4"/>
       <c r="C1132" s="4"/>
     </row>
-    <row r="1133" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1133" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1133" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="B1133" s="4" t="s">
-        <v>568</v>
-      </c>
+        <v>685</v>
+      </c>
+      <c r="B1133" s="4"/>
       <c r="C1133" s="4"/>
     </row>
     <row r="1134" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1134" s="3" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B1134" s="4" t="s">
         <v>568</v>
       </c>
       <c r="C1134" s="4"/>
     </row>
-    <row r="1135" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1135" s="21" t="s">
+    <row r="1135" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1135" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B1135" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C1135" s="4"/>
+    </row>
+    <row r="1136" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1136" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1136" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C1136" s="4"/>
+    </row>
+    <row r="1137" spans="1:3" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1137" s="21" t="s">
         <v>689</v>
       </c>
-      <c r="B1135" s="21"/>
-      <c r="C1135" s="21"/>
-    </row>
-    <row r="1136" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1136" s="3" t="s">
+      <c r="B1137" s="21"/>
+      <c r="C1137" s="21"/>
+    </row>
+    <row r="1138" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1138" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B1136" s="4" t="s">
+      <c r="B1138" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="C1136" s="4"/>
-    </row>
-    <row r="1137" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1137" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="B1137" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1137" s="4"/>
-    </row>
-    <row r="1138" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1138" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="B1138" s="4" t="s">
-        <v>693</v>
       </c>
       <c r="C1138" s="4"/>
     </row>
     <row r="1139" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1139" s="3" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B1139" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1139" s="4"/>
+    </row>
+    <row r="1140" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1140" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="B1140" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="C1139" s="4"/>
-    </row>
-    <row r="1140" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1140" s="3" t="s">
-        <v>1547</v>
-      </c>
-      <c r="B1140" s="4"/>
       <c r="C1140" s="4"/>
     </row>
     <row r="1141" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1141" s="3" t="s">
-        <v>1548</v>
+        <v>694</v>
       </c>
       <c r="B1141" s="4" t="s">
-        <v>355</v>
+        <v>693</v>
       </c>
       <c r="C1141" s="4"/>
     </row>
     <row r="1142" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1142" s="3" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="B1142" s="4"/>
       <c r="C1142" s="4"/>
     </row>
-    <row r="1143" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1143" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1143" s="3" t="s">
-        <v>1550</v>
-      </c>
-      <c r="B1143" s="4"/>
+        <v>1548</v>
+      </c>
+      <c r="B1143" s="4" t="s">
+        <v>355</v>
+      </c>
       <c r="C1143" s="4"/>
     </row>
     <row r="1144" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1144" s="3" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="B1144" s="4"/>
       <c r="C1144" s="4"/>
     </row>
-    <row r="1145" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1145" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1145" s="3" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="B1145" s="4"/>
       <c r="C1145" s="4"/>
     </row>
-    <row r="1146" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1146" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1146" s="3" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="B1146" s="4"/>
       <c r="C1146" s="4"/>
     </row>
-    <row r="1147" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1147" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1147" s="3" t="s">
-        <v>1554</v>
-      </c>
-      <c r="B1147" s="4" t="s">
-        <v>364</v>
-      </c>
+        <v>1552</v>
+      </c>
+      <c r="B1147" s="4"/>
       <c r="C1147" s="4"/>
     </row>
-    <row r="1148" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1148" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1148" s="3" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="B1148" s="4"/>
       <c r="C1148" s="4"/>
     </row>
     <row r="1149" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1149" s="3" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="B1149" s="4" t="s">
         <v>364</v>
@@ -16538,88 +16586,86 @@
     </row>
     <row r="1150" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1150" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B1150" s="4"/>
+      <c r="C1150" s="4"/>
+    </row>
+    <row r="1151" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1151" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B1151" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C1151" s="4"/>
+    </row>
+    <row r="1152" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1152" s="3" t="s">
         <v>1557</v>
       </c>
-      <c r="B1150" s="4" t="s">
+      <c r="B1152" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C1150" s="4"/>
-    </row>
-    <row r="1151" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1151" s="3" t="s">
+      <c r="C1152" s="4"/>
+    </row>
+    <row r="1153" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1153" s="3" t="s">
         <v>1558</v>
       </c>
-      <c r="B1151" s="4" t="s">
+      <c r="B1153" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="C1151" s="4"/>
-    </row>
-    <row r="1152" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1152" s="3" t="s">
-        <v>1559</v>
-      </c>
-      <c r="B1152" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="C1152" s="4"/>
-    </row>
-    <row r="1153" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1153" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="B1153" s="4" t="s">
-        <v>693</v>
       </c>
       <c r="C1153" s="4"/>
     </row>
     <row r="1154" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1154" s="3" t="s">
-        <v>696</v>
+        <v>1559</v>
       </c>
       <c r="B1154" s="4" t="s">
-        <v>697</v>
+        <v>355</v>
       </c>
       <c r="C1154" s="4"/>
     </row>
     <row r="1155" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1155" s="3" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B1155" s="4" t="s">
-        <v>162</v>
+        <v>693</v>
       </c>
       <c r="C1155" s="4"/>
     </row>
     <row r="1156" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1156" s="3" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B1156" s="4" t="s">
-        <v>146</v>
+        <v>697</v>
       </c>
       <c r="C1156" s="4"/>
     </row>
-    <row r="1157" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1157" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1157" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B1157" s="4" t="s">
-        <v>364</v>
+        <v>162</v>
       </c>
       <c r="C1157" s="4"/>
     </row>
     <row r="1158" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1158" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B1158" s="4" t="s">
-        <v>364</v>
+        <v>146</v>
       </c>
       <c r="C1158" s="4"/>
     </row>
-    <row r="1159" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1159" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1159" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B1159" s="4" t="s">
         <v>364</v>
@@ -16628,43 +16674,43 @@
     </row>
     <row r="1160" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1160" s="3" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B1160" s="4" t="s">
-        <v>180</v>
+        <v>364</v>
       </c>
       <c r="C1160" s="4"/>
     </row>
     <row r="1161" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1161" s="3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B1161" s="4" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="C1161" s="4"/>
     </row>
     <row r="1162" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1162" s="3" t="s">
-        <v>1560</v>
+        <v>703</v>
       </c>
       <c r="B1162" s="4" t="s">
-        <v>332</v>
+        <v>180</v>
       </c>
       <c r="C1162" s="4"/>
     </row>
     <row r="1163" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1163" s="3" t="s">
-        <v>1561</v>
+        <v>704</v>
       </c>
       <c r="B1163" s="4" t="s">
         <v>332</v>
       </c>
       <c r="C1163" s="4"/>
     </row>
-    <row r="1164" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1164" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1164" s="3" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="B1164" s="4" t="s">
         <v>332</v>
@@ -16673,16 +16719,16 @@
     </row>
     <row r="1165" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1165" s="3" t="s">
-        <v>705</v>
+        <v>1561</v>
       </c>
       <c r="B1165" s="4" t="s">
         <v>332</v>
       </c>
       <c r="C1165" s="4"/>
     </row>
-    <row r="1166" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1166" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1166" s="3" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B1166" s="4" t="s">
         <v>332</v>
@@ -16691,16 +16737,16 @@
     </row>
     <row r="1167" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1167" s="3" t="s">
-        <v>1564</v>
+        <v>705</v>
       </c>
       <c r="B1167" s="4" t="s">
         <v>332</v>
       </c>
       <c r="C1167" s="4"/>
     </row>
-    <row r="1168" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1168" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1168" s="3" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="B1168" s="4" t="s">
         <v>332</v>
@@ -16709,7 +16755,7 @@
     </row>
     <row r="1169" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1169" s="3" t="s">
-        <v>711</v>
+        <v>1564</v>
       </c>
       <c r="B1169" s="4" t="s">
         <v>332</v>
@@ -16718,139 +16764,139 @@
     </row>
     <row r="1170" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1170" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B1170" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C1170" s="4"/>
+    </row>
+    <row r="1171" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1171" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="B1171" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C1171" s="4"/>
+    </row>
+    <row r="1172" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1172" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="B1170" s="4" t="s">
+      <c r="B1172" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="C1170" s="4"/>
-    </row>
-    <row r="1171" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1171" s="3" t="s">
+      <c r="C1172" s="4"/>
+    </row>
+    <row r="1173" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1173" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="B1171" s="4" t="s">
+      <c r="B1173" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="C1171" s="4"/>
-    </row>
-    <row r="1172" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1172" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="B1172" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C1172" s="4"/>
-    </row>
-    <row r="1173" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1173" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="B1173" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="C1173" s="4"/>
     </row>
     <row r="1174" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1174" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="B1174" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1174" s="4"/>
+    </row>
+    <row r="1175" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1175" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="B1174" s="4" t="s">
+      <c r="B1175" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1175" s="4"/>
+    </row>
+    <row r="1176" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1176" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1176" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C1174" s="4"/>
-    </row>
-    <row r="1175" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1175" s="21" t="s">
+      <c r="C1176" s="4"/>
+    </row>
+    <row r="1177" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1177" s="21" t="s">
         <v>712</v>
       </c>
-      <c r="B1175" s="21"/>
-      <c r="C1175" s="21"/>
-    </row>
-    <row r="1176" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1176" s="21" t="s">
+      <c r="B1177" s="21"/>
+      <c r="C1177" s="21"/>
+    </row>
+    <row r="1178" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1178" s="21" t="s">
         <v>713</v>
       </c>
-      <c r="B1176" s="21"/>
-      <c r="C1176" s="21"/>
-    </row>
-    <row r="1177" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1177" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="B1177" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1177" s="4"/>
-    </row>
-    <row r="1178" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1178" s="3" t="s">
-        <v>1566</v>
-      </c>
-      <c r="B1178" s="4"/>
-      <c r="C1178" s="4"/>
+      <c r="B1178" s="21"/>
+      <c r="C1178" s="21"/>
     </row>
     <row r="1179" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1179" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B1179" s="4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C1179" s="4"/>
     </row>
-    <row r="1180" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1180" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1180" s="3" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="B1180" s="4"/>
       <c r="C1180" s="4"/>
     </row>
-    <row r="1181" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1181" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1181" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="B1181" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1181" s="4"/>
+    </row>
+    <row r="1182" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1182" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B1182" s="4"/>
+      <c r="C1182" s="4"/>
+    </row>
+    <row r="1183" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1183" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="B1181" s="4"/>
-      <c r="C1181" s="4"/>
-    </row>
-    <row r="1182" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1182" s="14" t="s">
+      <c r="B1183" s="4"/>
+      <c r="C1183" s="4"/>
+    </row>
+    <row r="1184" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1184" s="14" t="s">
         <v>717</v>
       </c>
-      <c r="B1182" s="9"/>
-      <c r="C1182" s="4"/>
-    </row>
-    <row r="1183" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1183" s="15" t="s">
-        <v>718</v>
-      </c>
-      <c r="B1183" s="16" t="s">
-        <v>575</v>
-      </c>
-      <c r="C1183" s="4"/>
-    </row>
-    <row r="1184" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1184" s="15" t="s">
-        <v>719</v>
-      </c>
-      <c r="B1184" s="16" t="s">
-        <v>75</v>
-      </c>
+      <c r="B1184" s="9"/>
       <c r="C1184" s="4"/>
     </row>
     <row r="1185" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1185" s="15" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B1185" s="16" t="s">
-        <v>166</v>
+        <v>575</v>
       </c>
       <c r="C1185" s="4"/>
     </row>
     <row r="1186" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1186" s="15" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B1186" s="16" t="s">
         <v>75</v>
@@ -16859,2823 +16905,2901 @@
     </row>
     <row r="1187" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1187" s="15" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B1187" s="16" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="C1187" s="4"/>
     </row>
     <row r="1188" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1188" s="15" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B1188" s="16" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C1188" s="4"/>
     </row>
     <row r="1189" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1189" s="15" t="s">
-        <v>724</v>
-      </c>
-      <c r="B1189" s="16"/>
+        <v>722</v>
+      </c>
+      <c r="B1189" s="16" t="s">
+        <v>122</v>
+      </c>
       <c r="C1189" s="4"/>
     </row>
     <row r="1190" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1190" s="15" t="s">
-        <v>725</v>
-      </c>
-      <c r="B1190" s="16"/>
+        <v>723</v>
+      </c>
+      <c r="B1190" s="16" t="s">
+        <v>69</v>
+      </c>
       <c r="C1190" s="4"/>
     </row>
     <row r="1191" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1191" s="15" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B1191" s="16"/>
       <c r="C1191" s="4"/>
     </row>
     <row r="1192" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1192" s="15" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B1192" s="16"/>
       <c r="C1192" s="4"/>
     </row>
     <row r="1193" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1193" s="15" t="s">
-        <v>728</v>
-      </c>
-      <c r="B1193" s="16" t="s">
-        <v>5</v>
-      </c>
+        <v>726</v>
+      </c>
+      <c r="B1193" s="16"/>
       <c r="C1193" s="4"/>
     </row>
     <row r="1194" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1194" s="15" t="s">
-        <v>1568</v>
+        <v>727</v>
       </c>
       <c r="B1194" s="16"/>
       <c r="C1194" s="4"/>
     </row>
     <row r="1195" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1195" s="15" t="s">
-        <v>1569</v>
-      </c>
-      <c r="B1195" s="16"/>
+        <v>728</v>
+      </c>
+      <c r="B1195" s="16" t="s">
+        <v>5</v>
+      </c>
       <c r="C1195" s="4"/>
     </row>
     <row r="1196" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1196" s="15" t="s">
-        <v>1570</v>
-      </c>
-      <c r="B1196" s="16" t="s">
-        <v>11</v>
-      </c>
+        <v>1568</v>
+      </c>
+      <c r="B1196" s="16"/>
       <c r="C1196" s="4"/>
     </row>
     <row r="1197" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1197" s="15" t="s">
-        <v>729</v>
-      </c>
-      <c r="B1197" s="16" t="s">
-        <v>84</v>
-      </c>
+        <v>1569</v>
+      </c>
+      <c r="B1197" s="16"/>
       <c r="C1197" s="4"/>
     </row>
     <row r="1198" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1198" s="15" t="s">
-        <v>730</v>
+        <v>1570</v>
       </c>
       <c r="B1198" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1198" s="4"/>
+    </row>
+    <row r="1199" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1199" s="15" t="s">
+        <v>729</v>
+      </c>
+      <c r="B1199" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C1198" s="4"/>
-    </row>
-    <row r="1199" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1199" s="21" t="s">
-        <v>1571</v>
-      </c>
-      <c r="B1199" s="21"/>
-      <c r="C1199" s="21"/>
+      <c r="C1199" s="4"/>
     </row>
     <row r="1200" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1200" s="15" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1200" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1200" s="4"/>
+    </row>
+    <row r="1201" spans="1:7" s="24" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1201" s="23" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B1201" s="28"/>
+      <c r="C1201" s="26"/>
+      <c r="D1201" s="25"/>
+      <c r="E1201" s="25"/>
+      <c r="F1201" s="25"/>
+      <c r="G1201" s="25"/>
+    </row>
+    <row r="1202" spans="1:7" s="24" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1202" s="23" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B1202" s="28"/>
+      <c r="C1202" s="26"/>
+      <c r="D1202" s="25"/>
+      <c r="E1202" s="25"/>
+      <c r="F1202" s="25"/>
+      <c r="G1202" s="25"/>
+    </row>
+    <row r="1203" spans="1:7" s="24" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1203" s="23" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B1203" s="27"/>
+      <c r="C1203" s="27"/>
+      <c r="D1203" s="25"/>
+      <c r="E1203" s="25"/>
+      <c r="F1203" s="25"/>
+      <c r="G1203" s="25"/>
+    </row>
+    <row r="1204" spans="1:7" s="24" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1204" s="23" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1204" s="27"/>
+      <c r="C1204" s="27"/>
+      <c r="D1204" s="25"/>
+      <c r="E1204" s="25"/>
+      <c r="F1204" s="25"/>
+      <c r="G1204" s="25"/>
+    </row>
+    <row r="1205" spans="1:7" s="24" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1205" s="23" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B1205" s="27"/>
+      <c r="C1205" s="27"/>
+      <c r="D1205" s="25"/>
+      <c r="E1205" s="25"/>
+      <c r="F1205" s="25"/>
+      <c r="G1205" s="25"/>
+    </row>
+    <row r="1206" spans="1:7" s="24" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1206" s="23" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B1206" s="27"/>
+      <c r="C1206" s="27"/>
+      <c r="D1206" s="25"/>
+      <c r="E1206" s="25"/>
+      <c r="F1206" s="25"/>
+      <c r="G1206" s="25"/>
+    </row>
+    <row r="1207" spans="1:7" s="24" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1207" s="23" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B1207" s="27"/>
+      <c r="C1207" s="27"/>
+      <c r="D1207" s="25"/>
+      <c r="E1207" s="25"/>
+      <c r="F1207" s="25"/>
+      <c r="G1207" s="25"/>
+    </row>
+    <row r="1208" spans="1:7" s="24" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1208" s="23" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B1208" s="27"/>
+      <c r="C1208" s="27"/>
+      <c r="D1208" s="25"/>
+      <c r="E1208" s="25"/>
+      <c r="F1208" s="25"/>
+      <c r="G1208" s="25"/>
+    </row>
+    <row r="1209" spans="1:7" s="24" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1209" s="23" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B1209" s="27"/>
+      <c r="C1209" s="27"/>
+      <c r="D1209" s="25"/>
+      <c r="E1209" s="25"/>
+      <c r="F1209" s="25"/>
+      <c r="G1209" s="25"/>
+    </row>
+    <row r="1210" spans="1:7" s="24" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1210" s="23" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B1210" s="27"/>
+      <c r="C1210" s="27"/>
+      <c r="D1210" s="25"/>
+      <c r="E1210" s="25"/>
+      <c r="F1210" s="25"/>
+      <c r="G1210" s="25"/>
+    </row>
+    <row r="1211" spans="1:7" customFormat="1" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1211" s="21" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B1211" s="22"/>
+      <c r="C1211" s="22"/>
+    </row>
+    <row r="1212" spans="1:7" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1212" s="15" t="s">
         <v>1572</v>
       </c>
-      <c r="B1200" s="15" t="s">
+      <c r="B1212" s="15" t="s">
         <v>1190</v>
       </c>
-      <c r="C1200" s="15"/>
-    </row>
-    <row r="1201" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1201" s="15" t="s">
+      <c r="C1212" s="15"/>
+    </row>
+    <row r="1213" spans="1:7" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1213" s="15" t="s">
         <v>1573</v>
       </c>
-      <c r="B1201" s="15" t="s">
+      <c r="B1213" s="15" t="s">
         <v>1190</v>
       </c>
-      <c r="C1201" s="15"/>
-    </row>
-    <row r="1202" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1202" s="21" t="s">
+      <c r="C1213" s="15"/>
+    </row>
+    <row r="1214" spans="1:7" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1214" s="21" t="s">
         <v>731</v>
       </c>
-      <c r="B1202" s="21"/>
-      <c r="C1202" s="21"/>
-    </row>
-    <row r="1203" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1203" s="21" t="s">
+      <c r="B1214" s="22"/>
+      <c r="C1214" s="22"/>
+    </row>
+    <row r="1215" spans="1:7" customFormat="1" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1215" s="21" t="s">
         <v>732</v>
       </c>
-      <c r="B1203" s="21"/>
-      <c r="C1203" s="21"/>
-    </row>
-    <row r="1204" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1204" s="3" t="s">
+      <c r="B1215" s="22"/>
+      <c r="C1215" s="22"/>
+    </row>
+    <row r="1216" spans="1:7" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1216" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="B1204" s="4" t="s">
+      <c r="B1216" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="C1204" s="17"/>
-    </row>
-    <row r="1205" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1205" s="3" t="s">
+      <c r="C1216" s="17"/>
+    </row>
+    <row r="1217" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1217" s="3" t="s">
         <v>1574</v>
       </c>
-      <c r="B1205" s="4" t="s">
+      <c r="B1217" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="C1205" s="17"/>
-    </row>
-    <row r="1206" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1206" s="3" t="s">
+      <c r="C1217" s="17"/>
+    </row>
+    <row r="1218" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1218" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="B1206" s="4" t="s">
+      <c r="B1218" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="C1206" s="17"/>
-    </row>
-    <row r="1207" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1207" s="3" t="s">
+      <c r="C1218" s="17"/>
+    </row>
+    <row r="1219" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1219" s="3" t="s">
         <v>1575</v>
       </c>
-      <c r="B1207" s="4" t="s">
+      <c r="B1219" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="C1207" s="17"/>
-    </row>
-    <row r="1208" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1208" s="3" t="s">
+      <c r="C1219" s="17"/>
+    </row>
+    <row r="1220" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1220" s="3" t="s">
         <v>1576</v>
       </c>
-      <c r="B1208" s="4" t="s">
+      <c r="B1220" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C1208" s="17"/>
-    </row>
-    <row r="1209" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1209" s="21" t="s">
+      <c r="C1220" s="17"/>
+    </row>
+    <row r="1221" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1221" s="21" t="s">
         <v>736</v>
       </c>
-      <c r="B1209" s="21"/>
-      <c r="C1209" s="21"/>
-    </row>
-    <row r="1210" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1210" s="3" t="s">
+      <c r="B1221" s="21"/>
+      <c r="C1221" s="21"/>
+    </row>
+    <row r="1222" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1222" s="3" t="s">
         <v>1577</v>
       </c>
-      <c r="B1210" s="4" t="s">
+      <c r="B1222" s="4" t="s">
         <v>1578</v>
       </c>
-      <c r="C1210" s="17"/>
-    </row>
-    <row r="1211" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1211" s="21" t="s">
+      <c r="C1222" s="17"/>
+    </row>
+    <row r="1223" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1223" s="21" t="s">
         <v>737</v>
       </c>
-      <c r="B1211" s="21"/>
-      <c r="C1211" s="21"/>
-    </row>
-    <row r="1212" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1212" s="3" t="s">
+      <c r="B1223" s="21"/>
+      <c r="C1223" s="21"/>
+    </row>
+    <row r="1224" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1224" s="3" t="s">
         <v>1579</v>
       </c>
-      <c r="B1212" s="4" t="s">
+      <c r="B1224" s="4" t="s">
         <v>1580</v>
       </c>
-      <c r="C1212" s="17"/>
-    </row>
-    <row r="1213" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1213" s="3" t="s">
+      <c r="C1224" s="17"/>
+    </row>
+    <row r="1225" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1225" s="3" t="s">
         <v>1581</v>
       </c>
-      <c r="B1213" s="4" t="s">
+      <c r="B1225" s="4" t="s">
         <v>1580</v>
       </c>
-      <c r="C1213" s="17"/>
-    </row>
-    <row r="1214" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1214" s="3" t="s">
+      <c r="C1225" s="17"/>
+    </row>
+    <row r="1226" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1226" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="B1214" s="4" t="s">
+      <c r="B1226" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C1214" s="17"/>
-    </row>
-    <row r="1215" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1215" s="3" t="s">
+      <c r="C1226" s="17"/>
+    </row>
+    <row r="1227" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1227" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="B1215" s="4" t="s">
+      <c r="B1227" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C1215" s="17"/>
-    </row>
-    <row r="1216" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1216" s="21" t="s">
+      <c r="C1227" s="17"/>
+    </row>
+    <row r="1228" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1228" s="21" t="s">
         <v>741</v>
       </c>
-      <c r="B1216" s="21"/>
-      <c r="C1216" s="21"/>
-    </row>
-    <row r="1217" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1217" s="3" t="s">
+      <c r="B1228" s="21"/>
+      <c r="C1228" s="21"/>
+    </row>
+    <row r="1229" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1229" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="B1217" s="4" t="s">
+      <c r="B1229" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C1217" s="17"/>
-    </row>
-    <row r="1218" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1218" s="3" t="s">
+      <c r="C1229" s="17"/>
+    </row>
+    <row r="1230" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1230" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="B1218" s="4" t="s">
+      <c r="B1230" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C1218" s="17"/>
-    </row>
-    <row r="1219" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1219" s="3" t="s">
+      <c r="C1230" s="17"/>
+    </row>
+    <row r="1231" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1231" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="B1219" s="4" t="s">
+      <c r="B1231" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C1219" s="17"/>
-    </row>
-    <row r="1220" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1220" s="3" t="s">
+      <c r="C1231" s="17"/>
+    </row>
+    <row r="1232" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1232" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="B1220" s="4" t="s">
+      <c r="B1232" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C1220" s="17"/>
-    </row>
-    <row r="1221" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1221" s="3" t="s">
+      <c r="C1232" s="17"/>
+    </row>
+    <row r="1233" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1233" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="B1221" s="4" t="s">
+      <c r="B1233" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C1221" s="17"/>
-    </row>
-    <row r="1222" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1222" s="3" t="s">
+      <c r="C1233" s="17"/>
+    </row>
+    <row r="1234" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1234" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="B1222" s="4" t="s">
+      <c r="B1234" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C1222" s="17"/>
-    </row>
-    <row r="1223" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1223" s="3" t="s">
+      <c r="C1234" s="17"/>
+    </row>
+    <row r="1235" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1235" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="B1223" s="4" t="s">
+      <c r="B1235" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C1223" s="17"/>
-    </row>
-    <row r="1224" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1224" s="3" t="s">
+      <c r="C1235" s="17"/>
+    </row>
+    <row r="1236" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1236" s="3" t="s">
         <v>1582</v>
       </c>
-      <c r="B1224" s="4" t="s">
+      <c r="B1236" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C1224" s="17"/>
-    </row>
-    <row r="1225" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1225" s="3" t="s">
+      <c r="C1236" s="17"/>
+    </row>
+    <row r="1237" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1237" s="3" t="s">
         <v>1583</v>
       </c>
-      <c r="B1225" s="4" t="s">
+      <c r="B1237" s="4" t="s">
         <v>1584</v>
       </c>
-      <c r="C1225" s="17"/>
-    </row>
-    <row r="1226" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1226" s="3" t="s">
+      <c r="C1237" s="17"/>
+    </row>
+    <row r="1238" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1238" s="3" t="s">
         <v>1585</v>
       </c>
-      <c r="B1226" s="4" t="s">
+      <c r="B1238" s="4" t="s">
         <v>1586</v>
       </c>
-      <c r="C1226" s="17"/>
-    </row>
-    <row r="1227" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1227" s="3" t="s">
+      <c r="C1238" s="17"/>
+    </row>
+    <row r="1239" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1239" s="3" t="s">
         <v>1587</v>
       </c>
-      <c r="B1227" s="4" t="s">
+      <c r="B1239" s="4" t="s">
         <v>1586</v>
       </c>
-      <c r="C1227" s="17"/>
-    </row>
-    <row r="1228" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1228" s="3" t="s">
+      <c r="C1239" s="17"/>
+    </row>
+    <row r="1240" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1240" s="3" t="s">
         <v>749</v>
       </c>
-      <c r="B1228" s="4" t="s">
+      <c r="B1240" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C1228" s="17"/>
-    </row>
-    <row r="1229" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1229" s="3" t="s">
+      <c r="C1240" s="17"/>
+    </row>
+    <row r="1241" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1241" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="B1229" s="4" t="s">
+      <c r="B1241" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C1229" s="17"/>
-    </row>
-    <row r="1230" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1230" s="3" t="s">
+      <c r="C1241" s="17"/>
+    </row>
+    <row r="1242" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1242" s="3" t="s">
         <v>1588</v>
       </c>
-      <c r="B1230" s="4" t="s">
+      <c r="B1242" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C1230" s="17"/>
-    </row>
-    <row r="1231" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1231" s="3" t="s">
+      <c r="C1242" s="17"/>
+    </row>
+    <row r="1243" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1243" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="B1231" s="4" t="s">
+      <c r="B1243" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="C1231" s="4"/>
-    </row>
-    <row r="1232" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1232" s="3" t="s">
+      <c r="C1243" s="4"/>
+    </row>
+    <row r="1244" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1244" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="B1232" s="4" t="s">
+      <c r="B1244" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="C1232" s="4"/>
-    </row>
-    <row r="1233" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1233" s="3" t="s">
+      <c r="C1244" s="4"/>
+    </row>
+    <row r="1245" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1245" s="3" t="s">
         <v>1589</v>
       </c>
-      <c r="B1233" s="4" t="s">
+      <c r="B1245" s="4" t="s">
         <v>1590</v>
       </c>
-      <c r="C1233" s="17"/>
-    </row>
-    <row r="1234" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1234" s="3" t="s">
+      <c r="C1245" s="17"/>
+    </row>
+    <row r="1246" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1246" s="3" t="s">
         <v>1591</v>
       </c>
-      <c r="B1234" s="4" t="s">
+      <c r="B1246" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C1234" s="17"/>
-    </row>
-    <row r="1235" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1235" s="3" t="s">
+      <c r="C1246" s="17"/>
+    </row>
+    <row r="1247" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1247" s="3" t="s">
         <v>1592</v>
       </c>
-      <c r="B1235" s="4" t="s">
+      <c r="B1247" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C1235" s="17"/>
-    </row>
-    <row r="1236" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1236" s="3" t="s">
+      <c r="C1247" s="17"/>
+    </row>
+    <row r="1248" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1248" s="3" t="s">
         <v>1593</v>
       </c>
-      <c r="B1236" s="4" t="s">
+      <c r="B1248" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C1236" s="17"/>
-    </row>
-    <row r="1237" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1237" s="3" t="s">
+      <c r="C1248" s="17"/>
+    </row>
+    <row r="1249" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1249" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="B1237" s="4" t="s">
+      <c r="B1249" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C1237" s="17"/>
-    </row>
-    <row r="1238" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1238" s="3" t="s">
+      <c r="C1249" s="17"/>
+    </row>
+    <row r="1250" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1250" s="3" t="s">
         <v>1594</v>
       </c>
-      <c r="B1238" s="4" t="s">
+      <c r="B1250" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C1238" s="17"/>
-    </row>
-    <row r="1239" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1239" s="3" t="s">
+      <c r="C1250" s="17"/>
+    </row>
+    <row r="1251" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1251" s="3" t="s">
         <v>755</v>
       </c>
-      <c r="B1239" s="4" t="s">
+      <c r="B1251" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C1239" s="17"/>
-    </row>
-    <row r="1240" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1240" s="21" t="s">
+      <c r="C1251" s="17"/>
+    </row>
+    <row r="1252" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1252" s="21" t="s">
         <v>1595</v>
       </c>
-      <c r="B1240" s="21"/>
-      <c r="C1240" s="21"/>
-    </row>
-    <row r="1241" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1241" s="3" t="s">
+      <c r="B1252" s="21"/>
+      <c r="C1252" s="21"/>
+    </row>
+    <row r="1253" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1253" s="3" t="s">
         <v>1596</v>
       </c>
-      <c r="B1241" s="3" t="s">
+      <c r="B1253" s="3" t="s">
         <v>1597</v>
       </c>
-      <c r="C1241" s="17"/>
-    </row>
-    <row r="1242" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1242" s="21" t="s">
+      <c r="C1253" s="17"/>
+    </row>
+    <row r="1254" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1254" s="21" t="s">
         <v>756</v>
       </c>
-      <c r="B1242" s="21"/>
-      <c r="C1242" s="21"/>
-    </row>
-    <row r="1243" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1243" s="21" t="s">
+      <c r="B1254" s="21"/>
+      <c r="C1254" s="21"/>
+    </row>
+    <row r="1255" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1255" s="21" t="s">
         <v>757</v>
       </c>
-      <c r="B1243" s="21"/>
-      <c r="C1243" s="21"/>
-    </row>
-    <row r="1244" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1244" s="3" t="s">
+      <c r="B1255" s="21"/>
+      <c r="C1255" s="21"/>
+    </row>
+    <row r="1256" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1256" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="B1244" s="4">
+      <c r="B1256" s="4">
         <v>50</v>
       </c>
-      <c r="C1244" s="4"/>
-    </row>
-    <row r="1245" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1245" s="3" t="s">
+      <c r="C1256" s="4"/>
+    </row>
+    <row r="1257" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1257" s="3" t="s">
         <v>759</v>
       </c>
-      <c r="B1245" s="4">
+      <c r="B1257" s="4">
         <v>50</v>
       </c>
-      <c r="C1245" s="4"/>
-    </row>
-    <row r="1246" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1246" s="3" t="s">
+      <c r="C1257" s="4"/>
+    </row>
+    <row r="1258" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1258" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="B1246" s="4">
+      <c r="B1258" s="4">
         <v>50</v>
       </c>
-      <c r="C1246" s="4"/>
-    </row>
-    <row r="1247" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1247" s="3" t="s">
+      <c r="C1258" s="4"/>
+    </row>
+    <row r="1259" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1259" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="B1247" s="4">
+      <c r="B1259" s="4">
         <v>20</v>
       </c>
-      <c r="C1247" s="4"/>
-    </row>
-    <row r="1248" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1248" s="3" t="s">
+      <c r="C1259" s="4"/>
+    </row>
+    <row r="1260" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1260" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="B1248" s="4">
+      <c r="B1260" s="4">
         <v>20</v>
       </c>
-      <c r="C1248" s="4"/>
-    </row>
-    <row r="1249" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1249" s="3" t="s">
+      <c r="C1260" s="4"/>
+    </row>
+    <row r="1261" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1261" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="B1249" s="4">
+      <c r="B1261" s="4">
         <v>20</v>
       </c>
-      <c r="C1249" s="4"/>
-    </row>
-    <row r="1250" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1250" s="3" t="s">
+      <c r="C1261" s="4"/>
+    </row>
+    <row r="1262" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1262" s="3" t="s">
         <v>1697</v>
       </c>
-      <c r="B1250" s="4">
+      <c r="B1262" s="4">
         <v>1</v>
       </c>
-      <c r="C1250" s="4"/>
-    </row>
-    <row r="1251" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1251" s="3" t="s">
+      <c r="C1262" s="4"/>
+    </row>
+    <row r="1263" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1263" s="3" t="s">
         <v>1698</v>
       </c>
-      <c r="B1251" s="4">
+      <c r="B1263" s="4">
         <v>1</v>
       </c>
-      <c r="C1251" s="4"/>
-    </row>
-    <row r="1252" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1252" s="3" t="s">
+      <c r="C1263" s="4"/>
+    </row>
+    <row r="1264" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1264" s="3" t="s">
         <v>1699</v>
       </c>
-      <c r="B1252" s="4">
+      <c r="B1264" s="4">
         <v>1</v>
       </c>
-      <c r="C1252" s="4"/>
-    </row>
-    <row r="1253" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1253" s="21" t="s">
+      <c r="C1264" s="4"/>
+    </row>
+    <row r="1265" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1265" s="21" t="s">
         <v>764</v>
       </c>
-      <c r="B1253" s="21"/>
-      <c r="C1253" s="21"/>
-    </row>
-    <row r="1254" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1254" s="3" t="s">
+      <c r="B1265" s="21"/>
+      <c r="C1265" s="21"/>
+    </row>
+    <row r="1266" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1266" s="3" t="s">
         <v>1598</v>
       </c>
-      <c r="B1254" s="13" t="s">
+      <c r="B1266" s="13" t="s">
         <v>768</v>
       </c>
-      <c r="C1254" s="4"/>
-    </row>
-    <row r="1255" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1255" s="3" t="s">
+      <c r="C1266" s="4"/>
+    </row>
+    <row r="1267" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1267" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="B1255" s="13" t="s">
+      <c r="B1267" s="13" t="s">
         <v>766</v>
       </c>
-      <c r="C1255" s="4"/>
-    </row>
-    <row r="1256" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1256" s="3" t="s">
+      <c r="C1267" s="4"/>
+    </row>
+    <row r="1268" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1268" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="B1256" s="13" t="s">
+      <c r="B1268" s="13" t="s">
         <v>768</v>
       </c>
-      <c r="C1256" s="4"/>
-    </row>
-    <row r="1257" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1257" s="21" t="s">
+      <c r="C1268" s="4"/>
+    </row>
+    <row r="1269" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1269" s="21" t="s">
         <v>769</v>
       </c>
-      <c r="B1257" s="21"/>
-      <c r="C1257" s="21"/>
-    </row>
-    <row r="1258" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1258" s="3" t="s">
+      <c r="B1269" s="21"/>
+      <c r="C1269" s="21"/>
+    </row>
+    <row r="1270" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1270" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="B1258" s="4">
+      <c r="B1270" s="4">
         <v>100</v>
       </c>
-      <c r="C1258" s="4"/>
-    </row>
-    <row r="1259" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1259" s="3" t="s">
+      <c r="C1270" s="4"/>
+    </row>
+    <row r="1271" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1271" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="B1259" s="4">
+      <c r="B1271" s="4">
         <v>100</v>
       </c>
-      <c r="C1259" s="4"/>
-    </row>
-    <row r="1260" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1260" s="3" t="s">
+      <c r="C1271" s="4"/>
+    </row>
+    <row r="1272" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1272" s="3" t="s">
         <v>772</v>
       </c>
-      <c r="B1260" s="4">
+      <c r="B1272" s="4">
         <v>100</v>
       </c>
-      <c r="C1260" s="4"/>
-    </row>
-    <row r="1261" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1261" s="3" t="s">
+      <c r="C1272" s="4"/>
+    </row>
+    <row r="1273" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1273" s="3" t="s">
         <v>773</v>
       </c>
-      <c r="B1261" s="4">
+      <c r="B1273" s="4">
         <v>100</v>
       </c>
-      <c r="C1261" s="4"/>
-    </row>
-    <row r="1262" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1262" s="3" t="s">
+      <c r="C1273" s="4"/>
+    </row>
+    <row r="1274" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1274" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="B1262" s="4">
+      <c r="B1274" s="4">
         <v>100</v>
       </c>
-      <c r="C1262" s="4"/>
-    </row>
-    <row r="1263" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1263" s="3" t="s">
+      <c r="C1274" s="4"/>
+    </row>
+    <row r="1275" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1275" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="B1263" s="4">
+      <c r="B1275" s="4">
         <v>100</v>
       </c>
-      <c r="C1263" s="6"/>
-    </row>
-    <row r="1264" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1264" s="3" t="s">
+      <c r="C1275" s="6"/>
+    </row>
+    <row r="1276" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1276" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="B1264" s="4">
+      <c r="B1276" s="4">
         <v>50</v>
       </c>
-      <c r="C1264" s="6"/>
-    </row>
-    <row r="1265" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1265" s="3" t="s">
+      <c r="C1276" s="6"/>
+    </row>
+    <row r="1277" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1277" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="B1265" s="4">
+      <c r="B1277" s="4">
         <v>20</v>
       </c>
-      <c r="C1265" s="6"/>
-    </row>
-    <row r="1266" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1266" s="3" t="s">
+      <c r="C1277" s="6"/>
+    </row>
+    <row r="1278" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1278" s="3" t="s">
         <v>778</v>
       </c>
-      <c r="B1266" s="4">
+      <c r="B1278" s="4">
         <v>50</v>
       </c>
-      <c r="C1266" s="7"/>
-    </row>
-    <row r="1267" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1267" s="3" t="s">
+      <c r="C1278" s="7"/>
+    </row>
+    <row r="1279" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1279" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="B1267" s="4">
+      <c r="B1279" s="4">
         <v>10</v>
       </c>
-      <c r="C1267" s="4"/>
-    </row>
-    <row r="1268" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1268" s="3" t="s">
+      <c r="C1279" s="4"/>
+    </row>
+    <row r="1280" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1280" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="B1268" s="4">
+      <c r="B1280" s="4">
         <v>10</v>
       </c>
-      <c r="C1268" s="4"/>
-    </row>
-    <row r="1269" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1269" s="3" t="s">
+      <c r="C1280" s="4"/>
+    </row>
+    <row r="1281" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1281" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="B1269" s="4">
+      <c r="B1281" s="4">
         <v>10</v>
       </c>
-      <c r="C1269" s="4"/>
-    </row>
-    <row r="1270" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1270" s="21" t="s">
+      <c r="C1281" s="4"/>
+    </row>
+    <row r="1282" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1282" s="21" t="s">
         <v>782</v>
       </c>
-      <c r="B1270" s="21"/>
-      <c r="C1270" s="21"/>
-    </row>
-    <row r="1271" spans="1:3" ht="86.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1271" s="3" t="s">
+      <c r="B1282" s="21"/>
+      <c r="C1282" s="21"/>
+    </row>
+    <row r="1283" spans="1:3" customFormat="1" ht="86.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1283" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="B1271" s="4" t="s">
+      <c r="B1283" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="C1271" s="4"/>
-    </row>
-    <row r="1272" spans="1:3" ht="86.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1272" s="3" t="s">
+      <c r="C1283" s="4"/>
+    </row>
+    <row r="1284" spans="1:3" customFormat="1" ht="86.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1284" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="B1272" s="4" t="s">
+      <c r="B1284" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="C1272" s="4"/>
-    </row>
-    <row r="1273" spans="1:3" ht="101.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1273" s="3" t="s">
+      <c r="C1284" s="4"/>
+    </row>
+    <row r="1285" spans="1:3" customFormat="1" ht="101.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1285" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="B1273" s="4" t="s">
+      <c r="B1285" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="C1273" s="4"/>
-    </row>
-    <row r="1274" spans="1:3" ht="101.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1274" s="3" t="s">
+      <c r="C1285" s="4"/>
+    </row>
+    <row r="1286" spans="1:3" customFormat="1" ht="101.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1286" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="B1274" s="4" t="s">
+      <c r="B1286" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="C1274" s="4"/>
-    </row>
-    <row r="1275" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1275" s="21" t="s">
+      <c r="C1286" s="4"/>
+    </row>
+    <row r="1287" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1287" s="21" t="s">
         <v>788</v>
       </c>
-      <c r="B1275" s="21"/>
-      <c r="C1275" s="21"/>
-    </row>
-    <row r="1276" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1276" s="3" t="s">
+      <c r="B1287" s="21"/>
+      <c r="C1287" s="21"/>
+    </row>
+    <row r="1288" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1288" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="B1276" s="4" t="s">
+      <c r="B1288" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C1276" s="4"/>
-    </row>
-    <row r="1277" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1277" s="3" t="s">
+      <c r="C1288" s="4"/>
+    </row>
+    <row r="1289" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1289" s="3" t="s">
         <v>790</v>
-      </c>
-      <c r="B1277" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1277" s="4"/>
-    </row>
-    <row r="1278" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1278" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="B1278" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1278" s="4"/>
-    </row>
-    <row r="1279" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1279" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="B1279" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1279" s="4"/>
-    </row>
-    <row r="1280" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1280" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="B1280" s="4" t="s">
-        <v>794</v>
-      </c>
-      <c r="C1280" s="4"/>
-    </row>
-    <row r="1281" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1281" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="B1281" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1281" s="4"/>
-    </row>
-    <row r="1282" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1282" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="B1282" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1282" s="4"/>
-    </row>
-    <row r="1283" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1283" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="B1283" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1283" s="4"/>
-    </row>
-    <row r="1284" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1284" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="B1284" s="4" t="s">
-        <v>799</v>
-      </c>
-      <c r="C1284" s="4"/>
-    </row>
-    <row r="1285" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1285" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="B1285" s="4" t="s">
-        <v>801</v>
-      </c>
-      <c r="C1285" s="4"/>
-    </row>
-    <row r="1286" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1286" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="B1286" s="4" t="s">
-        <v>803</v>
-      </c>
-      <c r="C1286" s="4"/>
-    </row>
-    <row r="1287" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1287" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="B1287" s="4" t="s">
-        <v>804</v>
-      </c>
-      <c r="C1287" s="4"/>
-    </row>
-    <row r="1288" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1288" s="21" t="s">
-        <v>805</v>
-      </c>
-      <c r="B1288" s="21"/>
-      <c r="C1288" s="21"/>
-    </row>
-    <row r="1289" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1289" s="3" t="s">
-        <v>806</v>
       </c>
       <c r="B1289" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C1289" s="4"/>
     </row>
-    <row r="1290" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1290" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1290" s="3" t="s">
-        <v>807</v>
+        <v>791</v>
       </c>
       <c r="B1290" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C1290" s="4"/>
     </row>
-    <row r="1291" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1291" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1291" s="3" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="B1291" s="4" t="s">
-        <v>804</v>
+        <v>24</v>
       </c>
       <c r="C1291" s="4"/>
     </row>
-    <row r="1292" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1292" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1292" s="3" t="s">
-        <v>809</v>
+        <v>793</v>
       </c>
       <c r="B1292" s="4" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
       <c r="C1292" s="4"/>
     </row>
-    <row r="1293" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1293" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1293" s="3" t="s">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="B1293" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C1293" s="4"/>
     </row>
-    <row r="1294" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1294" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1294" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1294" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1294" s="4"/>
+    </row>
+    <row r="1295" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1295" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="B1295" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1295" s="4"/>
+    </row>
+    <row r="1296" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1296" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="B1296" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="C1296" s="4"/>
+    </row>
+    <row r="1297" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1297" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="B1297" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="C1297" s="4"/>
+    </row>
+    <row r="1298" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1298" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="B1298" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="C1298" s="4"/>
+    </row>
+    <row r="1299" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1299" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="B1299" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="C1299" s="4"/>
+    </row>
+    <row r="1300" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1300" s="21" t="s">
+        <v>805</v>
+      </c>
+      <c r="B1300" s="21"/>
+      <c r="C1300" s="21"/>
+    </row>
+    <row r="1301" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1301" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="B1301" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1301" s="4"/>
+    </row>
+    <row r="1302" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1302" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="B1302" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1302" s="4"/>
+    </row>
+    <row r="1303" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1303" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="B1303" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="C1303" s="4"/>
+    </row>
+    <row r="1304" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1304" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="B1304" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="C1304" s="4"/>
+    </row>
+    <row r="1305" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1305" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="B1305" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1305" s="4"/>
+    </row>
+    <row r="1306" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1306" s="3" t="s">
         <v>811</v>
       </c>
-      <c r="B1294" s="4" t="s">
+      <c r="B1306" s="4" t="s">
         <v>812</v>
       </c>
-      <c r="C1294" s="4"/>
-    </row>
-    <row r="1295" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1295" s="3" t="s">
+      <c r="C1306" s="4"/>
+    </row>
+    <row r="1307" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1307" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="B1295" s="4" t="s">
+      <c r="B1307" s="4" t="s">
         <v>814</v>
       </c>
-      <c r="C1295" s="4"/>
-    </row>
-    <row r="1296" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1296" s="21" t="s">
+      <c r="C1307" s="4"/>
+    </row>
+    <row r="1308" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1308" s="21" t="s">
         <v>815</v>
       </c>
-      <c r="B1296" s="21"/>
-      <c r="C1296" s="21"/>
-    </row>
-    <row r="1297" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1297" s="3" t="s">
+      <c r="B1308" s="21"/>
+      <c r="C1308" s="21"/>
+    </row>
+    <row r="1309" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1309" s="3" t="s">
         <v>816</v>
       </c>
-      <c r="B1297" s="4"/>
-      <c r="C1297" s="4"/>
-    </row>
-    <row r="1298" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1298" s="3" t="s">
+      <c r="B1309" s="4"/>
+      <c r="C1309" s="4"/>
+    </row>
+    <row r="1310" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1310" s="3" t="s">
         <v>1599</v>
       </c>
-      <c r="B1298" s="4" t="s">
+      <c r="B1310" s="4" t="s">
         <v>1600</v>
       </c>
-      <c r="C1298" s="4"/>
-    </row>
-    <row r="1299" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1299" s="3" t="s">
+      <c r="C1310" s="4"/>
+    </row>
+    <row r="1311" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1311" s="3" t="s">
         <v>817</v>
       </c>
-      <c r="B1299" s="4"/>
-      <c r="C1299" s="4"/>
-    </row>
-    <row r="1300" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1300" s="3" t="s">
+      <c r="B1311" s="4"/>
+      <c r="C1311" s="4"/>
+    </row>
+    <row r="1312" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1312" s="3" t="s">
         <v>1601</v>
       </c>
-      <c r="B1300" s="4"/>
-      <c r="C1300" s="4"/>
-    </row>
-    <row r="1301" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1301" s="3" t="s">
+      <c r="B1312" s="4"/>
+      <c r="C1312" s="4"/>
+    </row>
+    <row r="1313" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1313" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="B1301" s="4"/>
-      <c r="C1301" s="4"/>
-    </row>
-    <row r="1302" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1302" s="3" t="s">
+      <c r="B1313" s="4"/>
+      <c r="C1313" s="4"/>
+    </row>
+    <row r="1314" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1314" s="3" t="s">
         <v>819</v>
       </c>
-      <c r="B1302" s="4" t="s">
+      <c r="B1314" s="4" t="s">
         <v>820</v>
       </c>
-      <c r="C1302" s="4"/>
-    </row>
-    <row r="1303" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1303" s="3" t="s">
+      <c r="C1314" s="4"/>
+    </row>
+    <row r="1315" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1315" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="B1303" s="4"/>
-      <c r="C1303" s="4"/>
-    </row>
-    <row r="1304" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1304" s="3" t="s">
+      <c r="B1315" s="4"/>
+      <c r="C1315" s="4"/>
+    </row>
+    <row r="1316" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1316" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="B1304" s="4" t="s">
+      <c r="B1316" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="C1304" s="4"/>
-    </row>
-    <row r="1305" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1305" s="3" t="s">
+      <c r="C1316" s="4"/>
+    </row>
+    <row r="1317" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1317" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="B1305" s="4" t="s">
+      <c r="B1317" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="C1305" s="4"/>
-    </row>
-    <row r="1306" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1306" s="3" t="s">
+      <c r="C1317" s="4"/>
+    </row>
+    <row r="1318" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1318" s="3" t="s">
         <v>1602</v>
       </c>
-      <c r="B1306" s="4" t="s">
+      <c r="B1318" s="4" t="s">
         <v>1603</v>
       </c>
-      <c r="C1306" s="4"/>
-    </row>
-    <row r="1307" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1307" s="21" t="s">
+      <c r="C1318" s="4"/>
+    </row>
+    <row r="1319" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1319" s="21" t="s">
         <v>825</v>
       </c>
-      <c r="B1307" s="22"/>
-      <c r="C1307" s="22"/>
-    </row>
-    <row r="1308" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1308" s="3" t="s">
+      <c r="B1319" s="22"/>
+      <c r="C1319" s="22"/>
+    </row>
+    <row r="1320" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1320" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="B1308" s="4" t="s">
+      <c r="B1320" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C1308" s="4"/>
-    </row>
-    <row r="1309" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1309" s="3" t="s">
+      <c r="C1320" s="4"/>
+    </row>
+    <row r="1321" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1321" s="3" t="s">
         <v>1604</v>
       </c>
-      <c r="B1309" s="4" t="s">
+      <c r="B1321" s="4" t="s">
         <v>827</v>
       </c>
-      <c r="C1309" s="4"/>
-    </row>
-    <row r="1310" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1310" s="3" t="s">
+      <c r="C1321" s="4"/>
+    </row>
+    <row r="1322" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1322" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="B1310" s="4" t="s">
+      <c r="B1322" s="4" t="s">
         <v>1695</v>
       </c>
-      <c r="C1310" s="4"/>
-    </row>
-    <row r="1311" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1311" s="3" t="s">
+      <c r="C1322" s="4"/>
+    </row>
+    <row r="1323" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1323" s="3" t="s">
         <v>829</v>
       </c>
-      <c r="B1311" s="4" t="s">
+      <c r="B1323" s="4" t="s">
         <v>830</v>
       </c>
-      <c r="C1311" s="4"/>
-    </row>
-    <row r="1312" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1312" s="3" t="s">
+      <c r="C1323" s="4"/>
+    </row>
+    <row r="1324" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1324" s="3" t="s">
         <v>831</v>
       </c>
-      <c r="B1312" s="4" t="s">
+      <c r="B1324" s="4" t="s">
         <v>832</v>
       </c>
-      <c r="C1312" s="4"/>
-    </row>
-    <row r="1313" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1313" s="3" t="s">
+      <c r="C1324" s="4"/>
+    </row>
+    <row r="1325" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1325" s="3" t="s">
         <v>833</v>
       </c>
-      <c r="B1313" s="4" t="s">
+      <c r="B1325" s="4" t="s">
         <v>834</v>
       </c>
-      <c r="C1313" s="4"/>
-    </row>
-    <row r="1314" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1314" s="3" t="s">
+      <c r="C1325" s="4"/>
+    </row>
+    <row r="1326" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1326" s="3" t="s">
         <v>1605</v>
       </c>
-      <c r="B1314" s="4" t="s">
+      <c r="B1326" s="4" t="s">
         <v>1606</v>
       </c>
-      <c r="C1314" s="4"/>
-    </row>
-    <row r="1315" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1315" s="3" t="s">
+      <c r="C1326" s="4"/>
+    </row>
+    <row r="1327" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1327" s="3" t="s">
         <v>1607</v>
       </c>
-      <c r="B1315" s="4" t="s">
+      <c r="B1327" s="4" t="s">
         <v>1608</v>
       </c>
-      <c r="C1315" s="4"/>
-    </row>
-    <row r="1316" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1316" s="3" t="s">
+      <c r="C1327" s="4"/>
+    </row>
+    <row r="1328" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1328" s="3" t="s">
         <v>1609</v>
       </c>
-      <c r="B1316" s="4" t="s">
+      <c r="B1328" s="4" t="s">
         <v>1610</v>
       </c>
-      <c r="C1316" s="4"/>
-    </row>
-    <row r="1317" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1317" s="3" t="s">
+      <c r="C1328" s="4"/>
+    </row>
+    <row r="1329" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1329" s="3" t="s">
         <v>1611</v>
       </c>
-      <c r="B1317" s="4" t="s">
+      <c r="B1329" s="4" t="s">
         <v>1610</v>
       </c>
-      <c r="C1317" s="4"/>
-    </row>
-    <row r="1318" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1318" s="3" t="s">
+      <c r="C1329" s="4"/>
+    </row>
+    <row r="1330" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1330" s="3" t="s">
         <v>1612</v>
       </c>
-      <c r="B1318" s="4" t="s">
+      <c r="B1330" s="4" t="s">
         <v>1613</v>
       </c>
-      <c r="C1318" s="4"/>
-    </row>
-    <row r="1319" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1319" s="3" t="s">
+      <c r="C1330" s="4"/>
+    </row>
+    <row r="1331" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1331" s="3" t="s">
         <v>1614</v>
       </c>
-      <c r="B1319" s="4">
+      <c r="B1331" s="4">
         <v>1</v>
       </c>
-      <c r="C1319" s="4"/>
-    </row>
-    <row r="1320" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1320" s="3" t="s">
+      <c r="C1331" s="4"/>
+    </row>
+    <row r="1332" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1332" s="3" t="s">
         <v>1615</v>
       </c>
-      <c r="B1320" s="4" t="s">
+      <c r="B1332" s="4" t="s">
         <v>1616</v>
       </c>
-      <c r="C1320" s="4"/>
-    </row>
-    <row r="1321" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1321" s="3" t="s">
+      <c r="C1332" s="4"/>
+    </row>
+    <row r="1333" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1333" s="3" t="s">
         <v>1617</v>
       </c>
-      <c r="B1321" s="4" t="s">
+      <c r="B1333" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C1321" s="4"/>
-    </row>
-    <row r="1322" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1322" s="3" t="s">
+      <c r="C1333" s="4"/>
+    </row>
+    <row r="1334" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1334" s="3" t="s">
         <v>1618</v>
       </c>
-      <c r="B1322" s="4" t="s">
+      <c r="B1334" s="4" t="s">
         <v>837</v>
       </c>
-      <c r="C1322" s="4"/>
-    </row>
-    <row r="1323" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1323" s="3" t="s">
+      <c r="C1334" s="4"/>
+    </row>
+    <row r="1335" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1335" s="3" t="s">
         <v>1619</v>
       </c>
-      <c r="B1323" s="4" t="s">
+      <c r="B1335" s="4" t="s">
         <v>835</v>
       </c>
-      <c r="C1323" s="4"/>
-    </row>
-    <row r="1324" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1324" s="3" t="s">
+      <c r="C1335" s="4"/>
+    </row>
+    <row r="1336" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1336" s="3" t="s">
         <v>1620</v>
       </c>
-      <c r="B1324" s="4" t="s">
+      <c r="B1336" s="4" t="s">
         <v>1621</v>
       </c>
-      <c r="C1324" s="4"/>
-    </row>
-    <row r="1325" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1325" s="3" t="s">
+      <c r="C1336" s="4"/>
+    </row>
+    <row r="1337" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1337" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="B1325" s="4" t="s">
+      <c r="B1337" s="4" t="s">
         <v>837</v>
       </c>
-      <c r="C1325" s="4"/>
-    </row>
-    <row r="1326" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1326" s="21" t="s">
+      <c r="C1337" s="4"/>
+    </row>
+    <row r="1338" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1338" s="21" t="s">
         <v>838</v>
       </c>
-      <c r="B1326" s="21"/>
-      <c r="C1326" s="21"/>
-    </row>
-    <row r="1327" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1327" s="3" t="s">
+      <c r="B1338" s="21"/>
+      <c r="C1338" s="21"/>
+    </row>
+    <row r="1339" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1339" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="B1327" s="4" t="s">
+      <c r="B1339" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="C1327" s="4"/>
-    </row>
-    <row r="1328" spans="1:3" ht="86.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1328" s="3" t="s">
+      <c r="C1339" s="4"/>
+    </row>
+    <row r="1340" spans="1:3" customFormat="1" ht="86.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1340" s="3" t="s">
         <v>1622</v>
       </c>
-      <c r="B1328" s="4" t="s">
+      <c r="B1340" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="C1328" s="4"/>
-    </row>
-    <row r="1329" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1329" s="3" t="s">
+      <c r="C1340" s="4"/>
+    </row>
+    <row r="1341" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1341" s="3" t="s">
         <v>1623</v>
       </c>
-      <c r="B1329" s="4" t="s">
+      <c r="B1341" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="C1329" s="4"/>
-    </row>
-    <row r="1330" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1330" s="3" t="s">
+      <c r="C1341" s="4"/>
+    </row>
+    <row r="1342" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1342" s="3" t="s">
         <v>1624</v>
       </c>
-      <c r="B1330" s="4" t="s">
+      <c r="B1342" s="4" t="s">
         <v>1625</v>
       </c>
-      <c r="C1330" s="4"/>
-    </row>
-    <row r="1331" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1331" s="3" t="s">
+      <c r="C1342" s="4"/>
+    </row>
+    <row r="1343" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1343" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="B1331" s="4" t="s">
+      <c r="B1343" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="C1331" s="4"/>
-    </row>
-    <row r="1332" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1332" s="3" t="s">
+      <c r="C1343" s="4"/>
+    </row>
+    <row r="1344" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1344" s="3" t="s">
         <v>843</v>
       </c>
-      <c r="B1332" s="4" t="s">
+      <c r="B1344" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="C1332" s="4"/>
-    </row>
-    <row r="1333" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1333" s="3" t="s">
+      <c r="C1344" s="4"/>
+    </row>
+    <row r="1345" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1345" s="3" t="s">
         <v>1626</v>
       </c>
-      <c r="B1333" s="4" t="s">
+      <c r="B1345" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="C1333" s="4"/>
-    </row>
-    <row r="1334" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1334" s="3" t="s">
+      <c r="C1345" s="4"/>
+    </row>
+    <row r="1346" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1346" s="3" t="s">
         <v>1627</v>
       </c>
-      <c r="B1334" s="4" t="s">
+      <c r="B1346" s="4" t="s">
         <v>1603</v>
       </c>
-      <c r="C1334" s="4"/>
-    </row>
-    <row r="1335" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1335" s="3" t="s">
+      <c r="C1346" s="4"/>
+    </row>
+    <row r="1347" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1347" s="3" t="s">
         <v>1627</v>
       </c>
-      <c r="B1335" s="4" t="s">
+      <c r="B1347" s="4" t="s">
         <v>1628</v>
       </c>
-      <c r="C1335" s="4"/>
-    </row>
-    <row r="1336" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1336" s="3" t="s">
+      <c r="C1347" s="4"/>
+    </row>
+    <row r="1348" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1348" s="3" t="s">
         <v>1627</v>
       </c>
-      <c r="B1336" s="4" t="s">
+      <c r="B1348" s="4" t="s">
         <v>1629</v>
       </c>
-      <c r="C1336" s="4"/>
-    </row>
-    <row r="1337" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1337" s="3" t="s">
+      <c r="C1348" s="4"/>
+    </row>
+    <row r="1349" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1349" s="3" t="s">
         <v>1630</v>
       </c>
-      <c r="B1337" s="4"/>
-      <c r="C1337" s="4"/>
-    </row>
-    <row r="1338" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1338" s="3" t="s">
+      <c r="B1349" s="4"/>
+      <c r="C1349" s="4"/>
+    </row>
+    <row r="1350" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1350" s="3" t="s">
         <v>1631</v>
       </c>
-      <c r="B1338" s="4"/>
-      <c r="C1338" s="4"/>
-    </row>
-    <row r="1339" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1339" s="3" t="s">
+      <c r="B1350" s="4"/>
+      <c r="C1350" s="4"/>
+    </row>
+    <row r="1351" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1351" s="3" t="s">
         <v>1632</v>
       </c>
-      <c r="B1339" s="4" t="s">
+      <c r="B1351" s="4" t="s">
         <v>1633</v>
       </c>
-      <c r="C1339" s="4"/>
-    </row>
-    <row r="1340" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1340" s="3" t="s">
+      <c r="C1351" s="4"/>
+    </row>
+    <row r="1352" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1352" s="3" t="s">
         <v>1632</v>
       </c>
-      <c r="B1340" s="4" t="s">
+      <c r="B1352" s="4" t="s">
         <v>1634</v>
       </c>
-      <c r="C1340" s="4"/>
-    </row>
-    <row r="1341" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1341" s="3" t="s">
+      <c r="C1352" s="4"/>
+    </row>
+    <row r="1353" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1353" s="3" t="s">
         <v>1635</v>
       </c>
-      <c r="B1341" s="4" t="s">
+      <c r="B1353" s="4" t="s">
         <v>1636</v>
       </c>
-      <c r="C1341" s="4"/>
-    </row>
-    <row r="1342" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1342" s="3" t="s">
+      <c r="C1353" s="4"/>
+    </row>
+    <row r="1354" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1354" s="3" t="s">
         <v>1635</v>
       </c>
-      <c r="B1342" s="4" t="s">
+      <c r="B1354" s="4" t="s">
         <v>1637</v>
       </c>
-      <c r="C1342" s="4"/>
-    </row>
-    <row r="1343" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1343" s="3" t="s">
+      <c r="C1354" s="4"/>
+    </row>
+    <row r="1355" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1355" s="3" t="s">
         <v>1638</v>
       </c>
-      <c r="B1343" s="4" t="s">
+      <c r="B1355" s="4" t="s">
         <v>1636</v>
       </c>
-      <c r="C1343" s="4"/>
-    </row>
-    <row r="1344" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1344" s="3" t="s">
+      <c r="C1355" s="4"/>
+    </row>
+    <row r="1356" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1356" s="3" t="s">
         <v>1639</v>
       </c>
-      <c r="B1344" s="4" t="s">
+      <c r="B1356" s="4" t="s">
         <v>1640</v>
       </c>
-      <c r="C1344" s="4"/>
-    </row>
-    <row r="1345" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1345" s="3" t="s">
+      <c r="C1356" s="4"/>
+    </row>
+    <row r="1357" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1357" s="3" t="s">
         <v>1641</v>
       </c>
-      <c r="B1345" s="4" t="s">
+      <c r="B1357" s="4" t="s">
         <v>1642</v>
       </c>
-      <c r="C1345" s="4"/>
-    </row>
-    <row r="1346" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1346" s="3" t="s">
+      <c r="C1357" s="4"/>
+    </row>
+    <row r="1358" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1358" s="3" t="s">
         <v>1643</v>
       </c>
-      <c r="B1346" s="4" t="s">
+      <c r="B1358" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="C1346" s="4"/>
-    </row>
-    <row r="1347" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1347" s="3" t="s">
+      <c r="C1358" s="4"/>
+    </row>
+    <row r="1359" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1359" s="3" t="s">
         <v>1644</v>
       </c>
-      <c r="B1347" s="4" t="s">
+      <c r="B1359" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="C1347" s="4"/>
-    </row>
-    <row r="1348" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1348" s="3" t="s">
+      <c r="C1359" s="4"/>
+    </row>
+    <row r="1360" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1360" s="3" t="s">
         <v>1645</v>
       </c>
-      <c r="B1348" s="4" t="s">
+      <c r="B1360" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="C1348" s="4"/>
-    </row>
-    <row r="1349" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1349" s="3" t="s">
+      <c r="C1360" s="4"/>
+    </row>
+    <row r="1361" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1361" s="3" t="s">
         <v>1646</v>
       </c>
-      <c r="B1349" s="4" t="s">
+      <c r="B1361" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="C1349" s="4"/>
-    </row>
-    <row r="1350" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1350" s="3" t="s">
+      <c r="C1361" s="4"/>
+    </row>
+    <row r="1362" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1362" s="3" t="s">
         <v>1696</v>
       </c>
-      <c r="B1350" s="4" t="s">
+      <c r="B1362" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="C1350" s="4"/>
-    </row>
-    <row r="1351" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1351" s="3" t="s">
+      <c r="C1362" s="4"/>
+    </row>
+    <row r="1363" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1363" s="3" t="s">
         <v>1647</v>
       </c>
-      <c r="B1351" s="4" t="s">
+      <c r="B1363" s="4" t="s">
         <v>1629</v>
       </c>
-      <c r="C1351" s="4"/>
-    </row>
-    <row r="1352" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1352" s="3" t="s">
+      <c r="C1363" s="4"/>
+    </row>
+    <row r="1364" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1364" s="3" t="s">
         <v>1648</v>
       </c>
-      <c r="B1352" s="4" t="s">
+      <c r="B1364" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="C1352" s="4"/>
-    </row>
-    <row r="1353" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1353" s="3" t="s">
+      <c r="C1364" s="4"/>
+    </row>
+    <row r="1365" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1365" s="3" t="s">
         <v>1649</v>
       </c>
-      <c r="B1353" s="4">
+      <c r="B1365" s="4">
         <v>48</v>
       </c>
-      <c r="C1353" s="4"/>
-    </row>
-    <row r="1354" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1354" s="3" t="s">
+      <c r="C1365" s="4"/>
+    </row>
+    <row r="1366" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1366" s="3" t="s">
         <v>1650</v>
       </c>
-      <c r="B1354" s="4">
+      <c r="B1366" s="4">
         <v>24</v>
       </c>
-      <c r="C1354" s="4"/>
-    </row>
-    <row r="1355" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1355" s="3" t="s">
+      <c r="C1366" s="4"/>
+    </row>
+    <row r="1367" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1367" s="3" t="s">
         <v>844</v>
       </c>
-      <c r="B1355" s="4" t="s">
+      <c r="B1367" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="C1355" s="4"/>
-    </row>
-    <row r="1356" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1356" s="3" t="s">
+      <c r="C1367" s="4"/>
+    </row>
+    <row r="1368" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1368" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="B1356" s="4" t="s">
+      <c r="B1368" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C1356" s="4"/>
-    </row>
-    <row r="1357" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1357" s="21" t="s">
+      <c r="C1368" s="4"/>
+    </row>
+    <row r="1369" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1369" s="21" t="s">
         <v>847</v>
       </c>
-      <c r="B1357" s="21"/>
-      <c r="C1357" s="21"/>
-    </row>
-    <row r="1358" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1358" s="21" t="s">
+      <c r="B1369" s="21"/>
+      <c r="C1369" s="21"/>
+    </row>
+    <row r="1370" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1370" s="21" t="s">
         <v>848</v>
       </c>
-      <c r="B1358" s="21"/>
-      <c r="C1358" s="21"/>
-    </row>
-    <row r="1359" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1359" s="3" t="s">
+      <c r="B1370" s="21"/>
+      <c r="C1370" s="21"/>
+    </row>
+    <row r="1371" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1371" s="3" t="s">
         <v>849</v>
-      </c>
-      <c r="B1359" s="4" t="s">
-        <v>850</v>
-      </c>
-      <c r="C1359" s="4"/>
-    </row>
-    <row r="1360" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1360" s="3" t="s">
-        <v>851</v>
-      </c>
-      <c r="B1360" s="4" t="s">
-        <v>850</v>
-      </c>
-      <c r="C1360" s="4"/>
-    </row>
-    <row r="1361" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1361" s="3" t="s">
-        <v>852</v>
-      </c>
-      <c r="B1361" s="4" t="s">
-        <v>850</v>
-      </c>
-      <c r="C1361" s="4"/>
-    </row>
-    <row r="1362" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1362" s="3" t="s">
-        <v>853</v>
-      </c>
-      <c r="B1362" s="4" t="s">
-        <v>850</v>
-      </c>
-      <c r="C1362" s="4"/>
-    </row>
-    <row r="1363" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1363" s="3" t="s">
-        <v>854</v>
-      </c>
-      <c r="B1363" s="4" t="s">
-        <v>855</v>
-      </c>
-      <c r="C1363" s="4"/>
-    </row>
-    <row r="1364" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1364" s="3" t="s">
-        <v>856</v>
-      </c>
-      <c r="B1364" s="4" t="s">
-        <v>857</v>
-      </c>
-      <c r="C1364" s="4"/>
-    </row>
-    <row r="1365" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1365" s="3" t="s">
-        <v>849</v>
-      </c>
-      <c r="B1365" s="4" t="s">
-        <v>858</v>
-      </c>
-      <c r="C1365" s="4"/>
-    </row>
-    <row r="1366" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1366" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="B1366" s="4" t="s">
-        <v>858</v>
-      </c>
-      <c r="C1366" s="4"/>
-    </row>
-    <row r="1367" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1367" s="3" t="s">
-        <v>860</v>
-      </c>
-      <c r="B1367" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1367" s="4"/>
-    </row>
-    <row r="1368" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1368" s="3" t="s">
-        <v>861</v>
-      </c>
-      <c r="B1368" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1368" s="4"/>
-    </row>
-    <row r="1369" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1369" s="3" t="s">
-        <v>862</v>
-      </c>
-      <c r="B1369" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1369" s="4"/>
-    </row>
-    <row r="1370" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1370" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="B1370" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1370" s="4"/>
-    </row>
-    <row r="1371" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1371" s="3" t="s">
-        <v>864</v>
       </c>
       <c r="B1371" s="4" t="s">
         <v>850</v>
       </c>
       <c r="C1371" s="4"/>
     </row>
-    <row r="1372" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1372" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1372" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="B1372" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="C1372" s="4"/>
+    </row>
+    <row r="1373" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1373" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="B1373" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="C1373" s="4"/>
+    </row>
+    <row r="1374" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1374" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="B1374" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="C1374" s="4"/>
+    </row>
+    <row r="1375" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1375" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="B1375" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="C1375" s="4"/>
+    </row>
+    <row r="1376" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1376" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="B1376" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="C1376" s="4"/>
+    </row>
+    <row r="1377" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1377" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="B1377" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="C1377" s="4"/>
+    </row>
+    <row r="1378" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1378" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="B1378" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="C1378" s="4"/>
+    </row>
+    <row r="1379" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1379" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="B1379" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1379" s="4"/>
+    </row>
+    <row r="1380" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1380" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="B1380" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1380" s="4"/>
+    </row>
+    <row r="1381" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1381" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="B1381" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1381" s="4"/>
+    </row>
+    <row r="1382" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1382" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="B1382" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1382" s="4"/>
+    </row>
+    <row r="1383" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1383" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="B1383" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="C1383" s="4"/>
+    </row>
+    <row r="1384" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1384" s="3" t="s">
         <v>1651</v>
-      </c>
-      <c r="B1372" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1372" s="4"/>
-    </row>
-    <row r="1373" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1373" s="3" t="s">
-        <v>1652</v>
-      </c>
-      <c r="B1373" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1373" s="4"/>
-    </row>
-    <row r="1374" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1374" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="B1374" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1374" s="4"/>
-    </row>
-    <row r="1375" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1375" s="3" t="s">
-        <v>1653</v>
-      </c>
-      <c r="B1375" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1375" s="4"/>
-    </row>
-    <row r="1376" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1376" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="B1376" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1376" s="4"/>
-    </row>
-    <row r="1377" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1377" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="B1377" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1377" s="4"/>
-    </row>
-    <row r="1378" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1378" s="3" t="s">
-        <v>868</v>
-      </c>
-      <c r="B1378" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1378" s="4"/>
-    </row>
-    <row r="1379" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1379" s="3" t="s">
-        <v>869</v>
-      </c>
-      <c r="B1379" s="4" t="s">
-        <v>870</v>
-      </c>
-      <c r="C1379" s="4"/>
-    </row>
-    <row r="1380" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1380" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="B1380" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1380" s="4"/>
-    </row>
-    <row r="1381" spans="1:3" ht="101.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1381" s="3" t="s">
-        <v>1654</v>
-      </c>
-      <c r="B1381" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1381" s="4"/>
-    </row>
-    <row r="1382" spans="1:3" ht="101.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1382" s="3" t="s">
-        <v>1655</v>
-      </c>
-      <c r="B1382" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1382" s="4"/>
-    </row>
-    <row r="1383" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1383" s="3" t="s">
-        <v>1656</v>
-      </c>
-      <c r="B1383" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1383" s="4"/>
-    </row>
-    <row r="1384" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1384" s="3" t="s">
-        <v>1657</v>
       </c>
       <c r="B1384" s="4" t="s">
         <v>257</v>
       </c>
       <c r="C1384" s="4"/>
     </row>
-    <row r="1385" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1385" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1385" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B1385" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1385" s="4"/>
+    </row>
+    <row r="1386" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1386" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="B1386" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1386" s="4"/>
+    </row>
+    <row r="1387" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1387" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B1387" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1387" s="4"/>
+    </row>
+    <row r="1388" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1388" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="B1388" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1388" s="4"/>
+    </row>
+    <row r="1389" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1389" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="B1389" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1389" s="4"/>
+    </row>
+    <row r="1390" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1390" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="B1390" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1390" s="4"/>
+    </row>
+    <row r="1391" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1391" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="B1391" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="C1391" s="4"/>
+    </row>
+    <row r="1392" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1392" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B1392" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1392" s="4"/>
+    </row>
+    <row r="1393" spans="1:3" customFormat="1" ht="101.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1393" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B1393" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1393" s="4"/>
+    </row>
+    <row r="1394" spans="1:3" customFormat="1" ht="101.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1394" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B1394" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1394" s="4"/>
+    </row>
+    <row r="1395" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1395" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B1395" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1395" s="4"/>
+    </row>
+    <row r="1396" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1396" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B1396" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1396" s="4"/>
+    </row>
+    <row r="1397" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1397" s="3" t="s">
         <v>872</v>
-      </c>
-      <c r="B1385" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1385" s="4"/>
-    </row>
-    <row r="1386" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1386" s="3" t="s">
-        <v>873</v>
-      </c>
-      <c r="B1386" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1386" s="4"/>
-    </row>
-    <row r="1387" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1387" s="3" t="s">
-        <v>874</v>
-      </c>
-      <c r="B1387" s="4" t="s">
-        <v>870</v>
-      </c>
-      <c r="C1387" s="4"/>
-    </row>
-    <row r="1388" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1388" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="B1388" s="4" t="s">
-        <v>870</v>
-      </c>
-      <c r="C1388" s="4"/>
-    </row>
-    <row r="1389" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1389" s="3" t="s">
-        <v>876</v>
-      </c>
-      <c r="B1389" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1389" s="4"/>
-    </row>
-    <row r="1390" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1390" s="3" t="s">
-        <v>877</v>
-      </c>
-      <c r="B1390" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1390" s="4"/>
-    </row>
-    <row r="1391" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1391" s="21" t="s">
-        <v>878</v>
-      </c>
-      <c r="B1391" s="21"/>
-      <c r="C1391" s="21"/>
-    </row>
-    <row r="1392" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1392" s="21" t="s">
-        <v>879</v>
-      </c>
-      <c r="B1392" s="21"/>
-      <c r="C1392" s="21"/>
-    </row>
-    <row r="1393" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1393" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="B1393" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1393" s="4"/>
-    </row>
-    <row r="1394" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1394" s="3" t="s">
-        <v>881</v>
-      </c>
-      <c r="B1394" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1394" s="4"/>
-    </row>
-    <row r="1395" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1395" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="B1395" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1395" s="4"/>
-    </row>
-    <row r="1396" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1396" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="B1396" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1396" s="4"/>
-    </row>
-    <row r="1397" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1397" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="B1397" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1397" s="4"/>
     </row>
-    <row r="1398" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1398" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1398" s="3" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="B1398" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1398" s="4"/>
     </row>
-    <row r="1399" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1399" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1399" s="3" t="s">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="B1399" s="4" t="s">
-        <v>253</v>
+        <v>870</v>
       </c>
       <c r="C1399" s="4"/>
     </row>
-    <row r="1400" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1400" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1400" s="3" t="s">
-        <v>887</v>
+        <v>875</v>
       </c>
       <c r="B1400" s="4" t="s">
-        <v>253</v>
+        <v>870</v>
       </c>
       <c r="C1400" s="4"/>
     </row>
-    <row r="1401" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1401" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1401" s="3" t="s">
-        <v>888</v>
+        <v>876</v>
       </c>
       <c r="B1401" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C1401" s="4"/>
     </row>
-    <row r="1402" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1402" s="21" t="s">
-        <v>889</v>
-      </c>
-      <c r="B1402" s="21"/>
-      <c r="C1402" s="21"/>
-    </row>
-    <row r="1403" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1403" s="3" t="s">
-        <v>890</v>
-      </c>
-      <c r="B1403" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1403" s="4"/>
-    </row>
-    <row r="1404" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1404" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="B1404" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1404" s="4"/>
-    </row>
-    <row r="1405" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1402" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1402" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="B1402" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1402" s="4"/>
+    </row>
+    <row r="1403" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1403" s="21" t="s">
+        <v>878</v>
+      </c>
+      <c r="B1403" s="21"/>
+      <c r="C1403" s="21"/>
+    </row>
+    <row r="1404" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1404" s="21" t="s">
+        <v>879</v>
+      </c>
+      <c r="B1404" s="21"/>
+      <c r="C1404" s="21"/>
+    </row>
+    <row r="1405" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1405" s="3" t="s">
-        <v>892</v>
+        <v>880</v>
       </c>
       <c r="B1405" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1405" s="4"/>
     </row>
-    <row r="1406" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1406" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1406" s="3" t="s">
-        <v>893</v>
+        <v>881</v>
       </c>
       <c r="B1406" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1406" s="4"/>
     </row>
-    <row r="1407" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1407" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1407" s="3" t="s">
-        <v>894</v>
+        <v>882</v>
       </c>
       <c r="B1407" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1407" s="4"/>
     </row>
-    <row r="1408" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1408" s="8" t="s">
-        <v>895</v>
-      </c>
-      <c r="B1408" s="18" t="s">
+    <row r="1408" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1408" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="B1408" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1408" s="4"/>
     </row>
-    <row r="1409" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1409" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1409" s="3" t="s">
-        <v>896</v>
+        <v>884</v>
       </c>
       <c r="B1409" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1409" s="4"/>
     </row>
-    <row r="1410" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1410" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1410" s="3" t="s">
-        <v>897</v>
+        <v>885</v>
       </c>
       <c r="B1410" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1410" s="4"/>
     </row>
-    <row r="1411" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1411" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1411" s="3" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
       <c r="B1411" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1411" s="4"/>
     </row>
-    <row r="1412" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1412" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1412" s="3" t="s">
-        <v>899</v>
+        <v>887</v>
       </c>
       <c r="B1412" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1412" s="4"/>
     </row>
-    <row r="1413" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1413" s="19" t="s">
-        <v>900</v>
-      </c>
-      <c r="B1413" s="20" t="s">
+    <row r="1413" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1413" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="B1413" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C1413" s="20"/>
-    </row>
-    <row r="1414" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C1413" s="4"/>
+    </row>
+    <row r="1414" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1414" s="21" t="s">
-        <v>901</v>
+        <v>889</v>
       </c>
       <c r="B1414" s="21"/>
       <c r="C1414" s="21"/>
     </row>
-    <row r="1415" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1415" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1415" s="3" t="s">
-        <v>902</v>
+        <v>890</v>
       </c>
       <c r="B1415" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1415" s="4"/>
     </row>
-    <row r="1416" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1416" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1416" s="3" t="s">
-        <v>903</v>
+        <v>891</v>
       </c>
       <c r="B1416" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1416" s="4"/>
     </row>
-    <row r="1417" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1417" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1417" s="3" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
       <c r="B1417" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1417" s="4"/>
     </row>
-    <row r="1418" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1418" s="21" t="s">
-        <v>905</v>
-      </c>
-      <c r="B1418" s="21"/>
-      <c r="C1418" s="21"/>
-    </row>
-    <row r="1419" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1418" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1418" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1418" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1418" s="4"/>
+    </row>
+    <row r="1419" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1419" s="3" t="s">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="B1419" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1419" s="4"/>
     </row>
-    <row r="1420" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1420" s="3" t="s">
-        <v>906</v>
-      </c>
-      <c r="B1420" s="4" t="s">
+    <row r="1420" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1420" s="8" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1420" s="18" t="s">
         <v>253</v>
       </c>
       <c r="C1420" s="4"/>
     </row>
-    <row r="1421" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1421" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1421" s="3" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
       <c r="B1421" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1421" s="4"/>
     </row>
-    <row r="1422" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1422" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1422" s="3" t="s">
-        <v>908</v>
+        <v>897</v>
       </c>
       <c r="B1422" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1422" s="4"/>
     </row>
-    <row r="1423" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1423" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1423" s="3" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="B1423" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1423" s="4"/>
     </row>
-    <row r="1424" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1424" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1424" s="3" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="B1424" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1424" s="4"/>
     </row>
-    <row r="1425" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1425" s="3" t="s">
-        <v>909</v>
-      </c>
-      <c r="B1425" s="4" t="s">
+    <row r="1425" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1425" s="19" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1425" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="C1425" s="4"/>
-    </row>
-    <row r="1426" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1426" s="3" t="s">
-        <v>910</v>
-      </c>
-      <c r="B1426" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1426" s="4"/>
-    </row>
-    <row r="1427" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C1425" s="20"/>
+    </row>
+    <row r="1426" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1426" s="21" t="s">
+        <v>901</v>
+      </c>
+      <c r="B1426" s="21"/>
+      <c r="C1426" s="21"/>
+    </row>
+    <row r="1427" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1427" s="3" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="B1427" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1427" s="4"/>
     </row>
-    <row r="1428" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1428" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1428" s="3" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="B1428" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1428" s="4"/>
     </row>
-    <row r="1429" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1429" s="19" t="s">
-        <v>913</v>
-      </c>
-      <c r="B1429" s="20" t="s">
+    <row r="1429" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1429" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="B1429" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C1429" s="20"/>
-    </row>
-    <row r="1430" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C1429" s="4"/>
+    </row>
+    <row r="1430" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1430" s="21" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="B1430" s="21"/>
       <c r="C1430" s="21"/>
     </row>
-    <row r="1431" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1431" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1431" s="3" t="s">
-        <v>915</v>
+        <v>880</v>
       </c>
       <c r="B1431" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1431" s="4"/>
     </row>
-    <row r="1432" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1432" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1432" s="3" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B1432" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1432" s="4"/>
     </row>
-    <row r="1433" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1433" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1433" s="3" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="B1433" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1433" s="4"/>
     </row>
-    <row r="1434" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1434" s="19" t="s">
-        <v>918</v>
-      </c>
-      <c r="B1434" s="20" t="s">
+    <row r="1434" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1434" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="B1434" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C1434" s="20"/>
-    </row>
-    <row r="1435" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1435" s="21" t="s">
-        <v>919</v>
-      </c>
-      <c r="B1435" s="21"/>
-      <c r="C1435" s="21"/>
-    </row>
-    <row r="1436" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C1434" s="4"/>
+    </row>
+    <row r="1435" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1435" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="B1435" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1435" s="4"/>
+    </row>
+    <row r="1436" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1436" s="3" t="s">
-        <v>920</v>
+        <v>885</v>
       </c>
       <c r="B1436" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1436" s="4"/>
     </row>
-    <row r="1437" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1437" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1437" s="3" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="B1437" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C1437" s="7"/>
-    </row>
-    <row r="1438" spans="1:3" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="C1437" s="4"/>
+    </row>
+    <row r="1438" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1438" s="3" t="s">
-        <v>922</v>
+        <v>910</v>
       </c>
       <c r="B1438" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C1438" s="7"/>
-    </row>
-    <row r="1439" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="C1438" s="4"/>
+    </row>
+    <row r="1439" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1439" s="3" t="s">
-        <v>923</v>
-      </c>
-      <c r="B1439" s="4"/>
-      <c r="C1439" s="7"/>
-    </row>
-    <row r="1440" spans="1:3" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
+        <v>911</v>
+      </c>
+      <c r="B1439" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1439" s="4"/>
+    </row>
+    <row r="1440" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1440" s="3" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="B1440" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C1440" s="7"/>
-    </row>
-    <row r="1441" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1441" s="3" t="s">
-        <v>925</v>
-      </c>
-      <c r="B1441" s="11" t="s">
-        <v>926</v>
-      </c>
-      <c r="C1441" s="7"/>
-    </row>
-    <row r="1442" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1442" s="3" t="s">
-        <v>927</v>
-      </c>
-      <c r="B1442" s="11" t="s">
-        <v>926</v>
-      </c>
-      <c r="C1442" s="7"/>
-    </row>
-    <row r="1443" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="C1440" s="4"/>
+    </row>
+    <row r="1441" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1441" s="19" t="s">
+        <v>913</v>
+      </c>
+      <c r="B1441" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1441" s="20"/>
+    </row>
+    <row r="1442" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1442" s="21" t="s">
+        <v>914</v>
+      </c>
+      <c r="B1442" s="21"/>
+      <c r="C1442" s="21"/>
+    </row>
+    <row r="1443" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1443" s="3" t="s">
-        <v>928</v>
-      </c>
-      <c r="B1443" s="11" t="s">
-        <v>926</v>
-      </c>
-      <c r="C1443" s="7"/>
-    </row>
-    <row r="1444" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1444" s="21" t="s">
-        <v>929</v>
-      </c>
-      <c r="B1444" s="21"/>
-      <c r="C1444" s="21"/>
-    </row>
-    <row r="1445" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+        <v>915</v>
+      </c>
+      <c r="B1443" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1443" s="4"/>
+    </row>
+    <row r="1444" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1444" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="B1444" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1444" s="4"/>
+    </row>
+    <row r="1445" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1445" s="3" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="B1445" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C1445" s="7"/>
-    </row>
-    <row r="1446" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1446" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="B1446" s="4" t="s">
+      <c r="C1445" s="4"/>
+    </row>
+    <row r="1446" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1446" s="19" t="s">
+        <v>918</v>
+      </c>
+      <c r="B1446" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="C1446" s="7"/>
-    </row>
-    <row r="1447" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C1446" s="20"/>
+    </row>
+    <row r="1447" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1447" s="21" t="s">
-        <v>931</v>
+        <v>919</v>
       </c>
       <c r="B1447" s="21"/>
       <c r="C1447" s="21"/>
     </row>
-    <row r="1448" spans="1:3" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1448" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1448" s="3" t="s">
-        <v>932</v>
+        <v>920</v>
       </c>
       <c r="B1448" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C1448" s="7"/>
-    </row>
-    <row r="1449" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1449" s="21" t="s">
-        <v>1658</v>
-      </c>
-      <c r="B1449" s="21"/>
-      <c r="C1449" s="21"/>
-    </row>
-    <row r="1450" spans="1:3" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="C1448" s="4"/>
+    </row>
+    <row r="1449" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1449" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="B1449" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1449" s="7"/>
+    </row>
+    <row r="1450" spans="1:3" customFormat="1" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1450" s="3" t="s">
-        <v>1659</v>
+        <v>922</v>
       </c>
       <c r="B1450" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1450" s="7"/>
     </row>
-    <row r="1451" spans="1:3" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1451" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1451" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="B1451" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="B1451" s="4"/>
+      <c r="C1451" s="7"/>
+    </row>
+    <row r="1452" spans="1:3" customFormat="1" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1452" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="B1452" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C1451" s="7"/>
-    </row>
-    <row r="1452" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1452" s="21" t="s">
-        <v>933</v>
-      </c>
-      <c r="B1452" s="21"/>
-      <c r="C1452" s="21"/>
-    </row>
-    <row r="1453" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="C1452" s="7"/>
+    </row>
+    <row r="1453" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1453" s="3" t="s">
-        <v>934</v>
-      </c>
-      <c r="B1453" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="B1453" s="11" t="s">
+        <v>926</v>
+      </c>
+      <c r="C1453" s="7"/>
+    </row>
+    <row r="1454" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1454" s="3" t="s">
+        <v>927</v>
+      </c>
+      <c r="B1454" s="11" t="s">
+        <v>926</v>
+      </c>
+      <c r="C1454" s="7"/>
+    </row>
+    <row r="1455" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1455" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B1455" s="11" t="s">
+        <v>926</v>
+      </c>
+      <c r="C1455" s="7"/>
+    </row>
+    <row r="1456" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1456" s="21" t="s">
+        <v>929</v>
+      </c>
+      <c r="B1456" s="21"/>
+      <c r="C1456" s="21"/>
+    </row>
+    <row r="1457" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1457" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="B1457" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C1453" s="7"/>
-    </row>
-    <row r="1454" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1454" s="3" t="s">
-        <v>935</v>
-      </c>
-      <c r="B1454" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1454" s="7"/>
-    </row>
-    <row r="1455" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1455" s="3" t="s">
-        <v>936</v>
-      </c>
-      <c r="B1455" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1455" s="7"/>
-    </row>
-    <row r="1456" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1456" s="3" t="s">
-        <v>937</v>
-      </c>
-      <c r="B1456" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1456" s="7"/>
-    </row>
-    <row r="1457" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1457" s="21" t="s">
-        <v>938</v>
-      </c>
-      <c r="B1457" s="21"/>
-      <c r="C1457" s="21"/>
-    </row>
-    <row r="1458" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="C1457" s="7"/>
+    </row>
+    <row r="1458" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1458" s="3" t="s">
-        <v>939</v>
+        <v>886</v>
       </c>
       <c r="B1458" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1458" s="7"/>
     </row>
-    <row r="1459" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1459" s="3" t="s">
-        <v>940</v>
-      </c>
-      <c r="B1459" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1459" s="7"/>
-    </row>
-    <row r="1460" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1459" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1459" s="21" t="s">
+        <v>931</v>
+      </c>
+      <c r="B1459" s="21"/>
+      <c r="C1459" s="21"/>
+    </row>
+    <row r="1460" spans="1:3" customFormat="1" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1460" s="3" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="B1460" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1460" s="7"/>
     </row>
-    <row r="1461" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1461" s="3" t="s">
-        <v>942</v>
-      </c>
-      <c r="B1461" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1461" s="7"/>
-    </row>
-    <row r="1462" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1461" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1461" s="21" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B1461" s="21"/>
+      <c r="C1461" s="21"/>
+    </row>
+    <row r="1462" spans="1:3" customFormat="1" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1462" s="3" t="s">
-        <v>943</v>
+        <v>1659</v>
       </c>
       <c r="B1462" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1462" s="7"/>
     </row>
-    <row r="1463" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1463" spans="1:3" customFormat="1" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1463" s="3" t="s">
-        <v>944</v>
+        <v>880</v>
       </c>
       <c r="B1463" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1463" s="7"/>
     </row>
-    <row r="1464" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1464" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="B1464" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1464" s="7"/>
-    </row>
-    <row r="1465" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1464" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1464" s="21" t="s">
+        <v>933</v>
+      </c>
+      <c r="B1464" s="21"/>
+      <c r="C1464" s="21"/>
+    </row>
+    <row r="1465" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1465" s="3" t="s">
-        <v>946</v>
+        <v>934</v>
       </c>
       <c r="B1465" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1465" s="7"/>
     </row>
-    <row r="1466" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1466" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1466" s="3" t="s">
-        <v>947</v>
+        <v>935</v>
       </c>
       <c r="B1466" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1466" s="7"/>
     </row>
-    <row r="1467" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1467" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1467" s="3" t="s">
-        <v>948</v>
+        <v>936</v>
       </c>
       <c r="B1467" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1467" s="7"/>
     </row>
-    <row r="1468" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1468" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1468" s="3" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="B1468" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1468" s="7"/>
     </row>
-    <row r="1469" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1469" s="3" t="s">
-        <v>950</v>
-      </c>
-      <c r="B1469" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1469" s="7"/>
-    </row>
-    <row r="1470" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1469" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1469" s="21" t="s">
+        <v>938</v>
+      </c>
+      <c r="B1469" s="21"/>
+      <c r="C1469" s="21"/>
+    </row>
+    <row r="1470" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1470" s="3" t="s">
-        <v>951</v>
+        <v>939</v>
       </c>
       <c r="B1470" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1470" s="7"/>
     </row>
-    <row r="1471" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1471" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1471" s="3" t="s">
-        <v>952</v>
+        <v>940</v>
       </c>
       <c r="B1471" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1471" s="7"/>
     </row>
-    <row r="1472" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1472" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1472" s="3" t="s">
-        <v>953</v>
+        <v>941</v>
       </c>
       <c r="B1472" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1472" s="7"/>
     </row>
-    <row r="1473" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1473" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1473" s="3" t="s">
-        <v>954</v>
+        <v>942</v>
       </c>
       <c r="B1473" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1473" s="7"/>
     </row>
-    <row r="1474" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1474" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1474" s="3" t="s">
-        <v>955</v>
+        <v>943</v>
       </c>
       <c r="B1474" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1474" s="7"/>
     </row>
-    <row r="1475" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1475" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1475" s="3" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
       <c r="B1475" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1475" s="7"/>
     </row>
-    <row r="1476" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1476" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1476" s="3" t="s">
-        <v>957</v>
+        <v>945</v>
       </c>
       <c r="B1476" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1476" s="7"/>
     </row>
-    <row r="1477" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1477" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1477" s="3" t="s">
-        <v>958</v>
+        <v>946</v>
       </c>
       <c r="B1477" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1477" s="7"/>
     </row>
-    <row r="1478" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1478" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1478" s="3" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="B1478" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1478" s="7"/>
     </row>
-    <row r="1479" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1479" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1479" s="3" t="s">
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="B1479" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1479" s="7"/>
     </row>
-    <row r="1480" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1480" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1480" s="3" t="s">
-        <v>961</v>
+        <v>949</v>
       </c>
       <c r="B1480" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1480" s="7"/>
     </row>
-    <row r="1481" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1481" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1481" s="3" t="s">
-        <v>962</v>
+        <v>950</v>
       </c>
       <c r="B1481" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1481" s="7"/>
     </row>
-    <row r="1482" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1482" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1482" s="3" t="s">
-        <v>963</v>
+        <v>951</v>
       </c>
       <c r="B1482" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1482" s="7"/>
     </row>
-    <row r="1483" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1483" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1483" s="3" t="s">
-        <v>964</v>
+        <v>952</v>
       </c>
       <c r="B1483" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1483" s="7"/>
     </row>
-    <row r="1484" spans="1:3" ht="72.3" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1484" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1484" s="3" t="s">
-        <v>965</v>
+        <v>953</v>
       </c>
       <c r="B1484" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1484" s="7"/>
     </row>
-    <row r="1485" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1485" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1485" s="3" t="s">
-        <v>966</v>
+        <v>954</v>
       </c>
       <c r="B1485" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1485" s="7"/>
     </row>
-    <row r="1486" spans="1:3" ht="101.1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1486" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1486" s="3" t="s">
-        <v>967</v>
+        <v>955</v>
       </c>
       <c r="B1486" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1486" s="7"/>
     </row>
-    <row r="1487" spans="1:3" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1487" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1487" s="3" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="B1487" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1487" s="7"/>
     </row>
-    <row r="1488" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1488" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1488" s="3" t="s">
-        <v>969</v>
+        <v>957</v>
       </c>
       <c r="B1488" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1488" s="7"/>
     </row>
-    <row r="1489" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1489" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1489" s="3" t="s">
-        <v>970</v>
+        <v>958</v>
       </c>
       <c r="B1489" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1489" s="7"/>
     </row>
-    <row r="1490" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1490" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1490" s="3" t="s">
-        <v>971</v>
+        <v>959</v>
       </c>
       <c r="B1490" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1490" s="7"/>
     </row>
-    <row r="1491" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1491" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
       <c r="A1491" s="3" t="s">
-        <v>972</v>
+        <v>960</v>
       </c>
       <c r="B1491" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C1491" s="7"/>
     </row>
-    <row r="1492" spans="1:3" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1492" s="21" t="s">
+    <row r="1492" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1492" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="B1492" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1492" s="7"/>
+    </row>
+    <row r="1493" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1493" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="B1493" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1493" s="7"/>
+    </row>
+    <row r="1494" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1494" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="B1494" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1494" s="7"/>
+    </row>
+    <row r="1495" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1495" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B1495" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1495" s="7"/>
+    </row>
+    <row r="1496" spans="1:3" customFormat="1" ht="72.3" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1496" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="B1496" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1496" s="7"/>
+    </row>
+    <row r="1497" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1497" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="B1497" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1497" s="7"/>
+    </row>
+    <row r="1498" spans="1:3" customFormat="1" ht="101.1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1498" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="B1498" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1498" s="7"/>
+    </row>
+    <row r="1499" spans="1:3" customFormat="1" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1499" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="B1499" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1499" s="7"/>
+    </row>
+    <row r="1500" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1500" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="B1500" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1500" s="7"/>
+    </row>
+    <row r="1501" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1501" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="B1501" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1501" s="7"/>
+    </row>
+    <row r="1502" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1502" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="B1502" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1502" s="7"/>
+    </row>
+    <row r="1503" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1503" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="B1503" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1503" s="7"/>
+    </row>
+    <row r="1504" spans="1:3" customFormat="1" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1504" s="21" t="s">
         <v>973</v>
       </c>
-      <c r="B1492" s="21"/>
-      <c r="C1492" s="21"/>
-    </row>
-    <row r="1493" spans="1:3" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1493" s="3" t="s">
+      <c r="B1504" s="21"/>
+      <c r="C1504" s="21"/>
+    </row>
+    <row r="1505" spans="1:3" customFormat="1" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1505" s="3" t="s">
         <v>974</v>
       </c>
-      <c r="B1493" s="4" t="s">
+      <c r="B1505" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="C1493" s="7"/>
-    </row>
-    <row r="1494" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1494" s="3" t="s">
+      <c r="C1505" s="7"/>
+    </row>
+    <row r="1506" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1506" s="3" t="s">
         <v>976</v>
       </c>
-      <c r="B1494" s="4" t="s">
+      <c r="B1506" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="C1494" s="7"/>
-    </row>
-    <row r="1495" spans="1:3" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1495" s="3" t="s">
+      <c r="C1506" s="7"/>
+    </row>
+    <row r="1507" spans="1:3" customFormat="1" ht="57.9" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1507" s="3" t="s">
         <v>977</v>
       </c>
-      <c r="B1495" s="4" t="s">
+      <c r="B1507" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="C1495" s="7"/>
-    </row>
-    <row r="1496" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1496" s="3" t="s">
+      <c r="C1507" s="7"/>
+    </row>
+    <row r="1508" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1508" s="3" t="s">
         <v>978</v>
       </c>
-      <c r="B1496" s="4" t="s">
+      <c r="B1508" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="C1496" s="7"/>
-    </row>
-    <row r="1497" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1497" s="3" t="s">
+      <c r="C1508" s="7"/>
+    </row>
+    <row r="1509" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1509" s="3" t="s">
         <v>979</v>
       </c>
-      <c r="B1497" s="4" t="s">
+      <c r="B1509" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="C1497" s="7"/>
-    </row>
-    <row r="1498" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1498" s="3" t="s">
+      <c r="C1509" s="7"/>
+    </row>
+    <row r="1510" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1510" s="3" t="s">
         <v>980</v>
       </c>
-      <c r="B1498" s="4" t="s">
+      <c r="B1510" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="C1498" s="7"/>
-    </row>
-    <row r="1499" spans="1:3" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1499" s="3" t="s">
+      <c r="C1510" s="7"/>
+    </row>
+    <row r="1511" spans="1:3" customFormat="1" ht="18.3" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1511" s="3" t="s">
         <v>981</v>
       </c>
-      <c r="B1499" s="4" t="s">
+      <c r="B1511" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="C1499" s="7"/>
-    </row>
-    <row r="1500" spans="1:3" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1500" s="3" t="s">
+      <c r="C1511" s="7"/>
+    </row>
+    <row r="1512" spans="1:3" customFormat="1" ht="29.1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1512" s="3" t="s">
         <v>982</v>
       </c>
-      <c r="B1500" s="4" t="s">
+      <c r="B1512" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C1500" s="7"/>
-    </row>
-    <row r="1501" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1501" s="3" t="s">
+      <c r="C1512" s="7"/>
+    </row>
+    <row r="1513" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1513" s="3" t="s">
         <v>983</v>
       </c>
-      <c r="B1501" s="4" t="s">
+      <c r="B1513" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C1501" s="7"/>
-    </row>
-    <row r="1502" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1502" s="3" t="s">
+      <c r="C1513" s="7"/>
+    </row>
+    <row r="1514" spans="1:3" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="A1514" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="B1502" s="4" t="s">
+      <c r="B1514" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C1502" s="7"/>
-    </row>
+      <c r="C1514" s="7"/>
+    </row>
+    <row r="1515" spans="1:3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="1516" spans="1:3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="A1447:C1447"/>
-    <mergeCell ref="A1449:C1449"/>
-    <mergeCell ref="A1452:C1452"/>
-    <mergeCell ref="A1457:C1457"/>
-    <mergeCell ref="A1492:C1492"/>
-    <mergeCell ref="A1444:C1444"/>
-    <mergeCell ref="A1253:C1253"/>
-    <mergeCell ref="A1257:C1257"/>
-    <mergeCell ref="A1270:C1270"/>
-    <mergeCell ref="A1275:C1275"/>
-    <mergeCell ref="A1288:C1288"/>
-    <mergeCell ref="A1296:C1296"/>
-    <mergeCell ref="A1307:C1307"/>
-    <mergeCell ref="A1326:C1326"/>
-    <mergeCell ref="A1357:C1357"/>
-    <mergeCell ref="A1358:C1358"/>
-    <mergeCell ref="A1391:C1391"/>
-    <mergeCell ref="A1392:C1392"/>
-    <mergeCell ref="A1402:C1402"/>
-    <mergeCell ref="A1414:C1414"/>
-    <mergeCell ref="A1209:C1209"/>
-    <mergeCell ref="A1211:C1211"/>
-    <mergeCell ref="A1418:C1418"/>
-    <mergeCell ref="A1430:C1430"/>
-    <mergeCell ref="A1435:C1435"/>
-    <mergeCell ref="A1216:C1216"/>
-    <mergeCell ref="A1240:C1240"/>
-    <mergeCell ref="A1242:C1242"/>
-    <mergeCell ref="A1243:C1243"/>
-    <mergeCell ref="A1075:C1075"/>
-    <mergeCell ref="A1080:C1080"/>
-    <mergeCell ref="A1083:C1083"/>
-    <mergeCell ref="A1084:C1084"/>
-    <mergeCell ref="A1089:C1089"/>
-    <mergeCell ref="A1105:C1105"/>
-    <mergeCell ref="A1135:C1135"/>
-    <mergeCell ref="A1175:C1175"/>
-    <mergeCell ref="A1176:C1176"/>
-    <mergeCell ref="A1199:C1199"/>
-    <mergeCell ref="A1202:C1202"/>
-    <mergeCell ref="A1203:C1203"/>
-    <mergeCell ref="A940:C940"/>
-    <mergeCell ref="A942:C942"/>
-    <mergeCell ref="A943:C943"/>
-    <mergeCell ref="A947:C947"/>
-    <mergeCell ref="A968:C968"/>
-    <mergeCell ref="A982:C982"/>
-    <mergeCell ref="A992:C992"/>
-    <mergeCell ref="A1027:C1027"/>
-    <mergeCell ref="A1032:C1032"/>
-    <mergeCell ref="A1039:C1039"/>
-    <mergeCell ref="A906:C906"/>
-    <mergeCell ref="A928:C928"/>
-    <mergeCell ref="A847:C847"/>
-    <mergeCell ref="A707:C707"/>
-    <mergeCell ref="A743:C743"/>
-    <mergeCell ref="A756:C756"/>
-    <mergeCell ref="A764:C764"/>
-    <mergeCell ref="A770:C770"/>
-    <mergeCell ref="A776:C776"/>
-    <mergeCell ref="A665:C665"/>
-    <mergeCell ref="A653:C653"/>
-    <mergeCell ref="A661:C661"/>
-    <mergeCell ref="A641:C641"/>
-    <mergeCell ref="A648:C648"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A333:C333"/>
+    <mergeCell ref="A375:C375"/>
+    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="A178:C178"/>
+    <mergeCell ref="A183:C183"/>
+    <mergeCell ref="A200:C200"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A277:C277"/>
     <mergeCell ref="A631:C631"/>
     <mergeCell ref="A632:C632"/>
     <mergeCell ref="A613:C613"/>
@@ -19690,19 +19814,71 @@
     <mergeCell ref="A570:C570"/>
     <mergeCell ref="A580:C580"/>
     <mergeCell ref="A593:C593"/>
-    <mergeCell ref="A333:C333"/>
-    <mergeCell ref="A375:C375"/>
-    <mergeCell ref="A130:C130"/>
-    <mergeCell ref="A178:C178"/>
-    <mergeCell ref="A183:C183"/>
-    <mergeCell ref="A200:C200"/>
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A277:C277"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A665:C665"/>
+    <mergeCell ref="A653:C653"/>
+    <mergeCell ref="A661:C661"/>
+    <mergeCell ref="A641:C641"/>
+    <mergeCell ref="A648:C648"/>
+    <mergeCell ref="A906:C906"/>
+    <mergeCell ref="A928:C928"/>
+    <mergeCell ref="A847:C847"/>
+    <mergeCell ref="A707:C707"/>
+    <mergeCell ref="A743:C743"/>
+    <mergeCell ref="A756:C756"/>
+    <mergeCell ref="A764:C764"/>
+    <mergeCell ref="A770:C770"/>
+    <mergeCell ref="A776:C776"/>
+    <mergeCell ref="A1214:C1214"/>
+    <mergeCell ref="A1215:C1215"/>
+    <mergeCell ref="A940:C940"/>
+    <mergeCell ref="A942:C942"/>
+    <mergeCell ref="A943:C943"/>
+    <mergeCell ref="A947:C947"/>
+    <mergeCell ref="A968:C968"/>
+    <mergeCell ref="A982:C982"/>
+    <mergeCell ref="A992:C992"/>
+    <mergeCell ref="A1027:C1027"/>
+    <mergeCell ref="A1032:C1032"/>
+    <mergeCell ref="A1039:C1039"/>
+    <mergeCell ref="A1105:C1105"/>
+    <mergeCell ref="A1137:C1137"/>
+    <mergeCell ref="A1177:C1177"/>
+    <mergeCell ref="A1178:C1178"/>
+    <mergeCell ref="A1211:C1211"/>
+    <mergeCell ref="A1075:C1075"/>
+    <mergeCell ref="A1080:C1080"/>
+    <mergeCell ref="A1083:C1083"/>
+    <mergeCell ref="A1084:C1084"/>
+    <mergeCell ref="A1089:C1089"/>
+    <mergeCell ref="A1221:C1221"/>
+    <mergeCell ref="A1223:C1223"/>
+    <mergeCell ref="A1430:C1430"/>
+    <mergeCell ref="A1442:C1442"/>
+    <mergeCell ref="A1447:C1447"/>
+    <mergeCell ref="A1228:C1228"/>
+    <mergeCell ref="A1252:C1252"/>
+    <mergeCell ref="A1254:C1254"/>
+    <mergeCell ref="A1255:C1255"/>
+    <mergeCell ref="A1456:C1456"/>
+    <mergeCell ref="A1265:C1265"/>
+    <mergeCell ref="A1269:C1269"/>
+    <mergeCell ref="A1282:C1282"/>
+    <mergeCell ref="A1287:C1287"/>
+    <mergeCell ref="A1300:C1300"/>
+    <mergeCell ref="A1308:C1308"/>
+    <mergeCell ref="A1319:C1319"/>
+    <mergeCell ref="A1338:C1338"/>
+    <mergeCell ref="A1369:C1369"/>
+    <mergeCell ref="A1370:C1370"/>
+    <mergeCell ref="A1403:C1403"/>
+    <mergeCell ref="A1404:C1404"/>
+    <mergeCell ref="A1414:C1414"/>
+    <mergeCell ref="A1426:C1426"/>
+    <mergeCell ref="A1459:C1459"/>
+    <mergeCell ref="A1461:C1461"/>
+    <mergeCell ref="A1464:C1464"/>
+    <mergeCell ref="A1469:C1469"/>
+    <mergeCell ref="A1504:C1504"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
